--- a/Platizio_Accreditation_Responses.xlsx
+++ b/Platizio_Accreditation_Responses.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG201"/>
+  <dimension ref="A1:AS201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -502,6 +502,18 @@
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="45" customWidth="1" min="32" max="32"/>
     <col width="45" customWidth="1" min="33" max="33"/>
+    <col width="28" customWidth="1" min="34" max="34"/>
+    <col width="28" customWidth="1" min="35" max="35"/>
+    <col width="28" customWidth="1" min="36" max="36"/>
+    <col width="45" customWidth="1" min="37" max="37"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="39" max="39"/>
+    <col width="28" customWidth="1" min="40" max="40"/>
+    <col width="28" customWidth="1" min="41" max="41"/>
+    <col width="28" customWidth="1" min="42" max="42"/>
+    <col width="28" customWidth="1" min="43" max="43"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -670,6 +682,66 @@
           <t>Gold / Jewellery Documents (Drive Links) [Hybrid]</t>
         </is>
       </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Account Type</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Aadhaar Number</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Certification Method</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Net Worth Certificate (Drive Link) [CA method]</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Spouse – Full Name</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Spouse – Organization</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Spouse – Email Address</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Spouse – Phone Number</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Spouse – PAN Number</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Spouse – Aadhaar Number</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Spouse – Current Address</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>Spouse – Permanent Address</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -705,6 +777,18 @@
       <c r="AE2" s="3" t="n"/>
       <c r="AF2" s="3" t="n"/>
       <c r="AG2" s="3" t="n"/>
+      <c r="AH2" s="3" t="n"/>
+      <c r="AI2" s="3" t="n"/>
+      <c r="AJ2" s="3" t="n"/>
+      <c r="AK2" s="3" t="n"/>
+      <c r="AL2" s="3" t="n"/>
+      <c r="AM2" s="3" t="n"/>
+      <c r="AN2" s="3" t="n"/>
+      <c r="AO2" s="3" t="n"/>
+      <c r="AP2" s="3" t="n"/>
+      <c r="AQ2" s="3" t="n"/>
+      <c r="AR2" s="3" t="n"/>
+      <c r="AS2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -740,6 +824,18 @@
       <c r="AE3" s="5" t="n"/>
       <c r="AF3" s="5" t="n"/>
       <c r="AG3" s="5" t="n"/>
+      <c r="AH3" s="5" t="n"/>
+      <c r="AI3" s="5" t="n"/>
+      <c r="AJ3" s="5" t="n"/>
+      <c r="AK3" s="5" t="n"/>
+      <c r="AL3" s="5" t="n"/>
+      <c r="AM3" s="5" t="n"/>
+      <c r="AN3" s="5" t="n"/>
+      <c r="AO3" s="5" t="n"/>
+      <c r="AP3" s="5" t="n"/>
+      <c r="AQ3" s="5" t="n"/>
+      <c r="AR3" s="5" t="n"/>
+      <c r="AS3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -775,6 +871,18 @@
       <c r="AE4" s="3" t="n"/>
       <c r="AF4" s="3" t="n"/>
       <c r="AG4" s="3" t="n"/>
+      <c r="AH4" s="3" t="n"/>
+      <c r="AI4" s="3" t="n"/>
+      <c r="AJ4" s="3" t="n"/>
+      <c r="AK4" s="3" t="n"/>
+      <c r="AL4" s="3" t="n"/>
+      <c r="AM4" s="3" t="n"/>
+      <c r="AN4" s="3" t="n"/>
+      <c r="AO4" s="3" t="n"/>
+      <c r="AP4" s="3" t="n"/>
+      <c r="AQ4" s="3" t="n"/>
+      <c r="AR4" s="3" t="n"/>
+      <c r="AS4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n"/>
@@ -810,6 +918,18 @@
       <c r="AE5" s="5" t="n"/>
       <c r="AF5" s="5" t="n"/>
       <c r="AG5" s="5" t="n"/>
+      <c r="AH5" s="5" t="n"/>
+      <c r="AI5" s="5" t="n"/>
+      <c r="AJ5" s="5" t="n"/>
+      <c r="AK5" s="5" t="n"/>
+      <c r="AL5" s="5" t="n"/>
+      <c r="AM5" s="5" t="n"/>
+      <c r="AN5" s="5" t="n"/>
+      <c r="AO5" s="5" t="n"/>
+      <c r="AP5" s="5" t="n"/>
+      <c r="AQ5" s="5" t="n"/>
+      <c r="AR5" s="5" t="n"/>
+      <c r="AS5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -845,6 +965,18 @@
       <c r="AE6" s="3" t="n"/>
       <c r="AF6" s="3" t="n"/>
       <c r="AG6" s="3" t="n"/>
+      <c r="AH6" s="3" t="n"/>
+      <c r="AI6" s="3" t="n"/>
+      <c r="AJ6" s="3" t="n"/>
+      <c r="AK6" s="3" t="n"/>
+      <c r="AL6" s="3" t="n"/>
+      <c r="AM6" s="3" t="n"/>
+      <c r="AN6" s="3" t="n"/>
+      <c r="AO6" s="3" t="n"/>
+      <c r="AP6" s="3" t="n"/>
+      <c r="AQ6" s="3" t="n"/>
+      <c r="AR6" s="3" t="n"/>
+      <c r="AS6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n"/>
@@ -880,6 +1012,18 @@
       <c r="AE7" s="5" t="n"/>
       <c r="AF7" s="5" t="n"/>
       <c r="AG7" s="5" t="n"/>
+      <c r="AH7" s="5" t="n"/>
+      <c r="AI7" s="5" t="n"/>
+      <c r="AJ7" s="5" t="n"/>
+      <c r="AK7" s="5" t="n"/>
+      <c r="AL7" s="5" t="n"/>
+      <c r="AM7" s="5" t="n"/>
+      <c r="AN7" s="5" t="n"/>
+      <c r="AO7" s="5" t="n"/>
+      <c r="AP7" s="5" t="n"/>
+      <c r="AQ7" s="5" t="n"/>
+      <c r="AR7" s="5" t="n"/>
+      <c r="AS7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -915,6 +1059,18 @@
       <c r="AE8" s="3" t="n"/>
       <c r="AF8" s="3" t="n"/>
       <c r="AG8" s="3" t="n"/>
+      <c r="AH8" s="3" t="n"/>
+      <c r="AI8" s="3" t="n"/>
+      <c r="AJ8" s="3" t="n"/>
+      <c r="AK8" s="3" t="n"/>
+      <c r="AL8" s="3" t="n"/>
+      <c r="AM8" s="3" t="n"/>
+      <c r="AN8" s="3" t="n"/>
+      <c r="AO8" s="3" t="n"/>
+      <c r="AP8" s="3" t="n"/>
+      <c r="AQ8" s="3" t="n"/>
+      <c r="AR8" s="3" t="n"/>
+      <c r="AS8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n"/>
@@ -950,6 +1106,18 @@
       <c r="AE9" s="5" t="n"/>
       <c r="AF9" s="5" t="n"/>
       <c r="AG9" s="5" t="n"/>
+      <c r="AH9" s="5" t="n"/>
+      <c r="AI9" s="5" t="n"/>
+      <c r="AJ9" s="5" t="n"/>
+      <c r="AK9" s="5" t="n"/>
+      <c r="AL9" s="5" t="n"/>
+      <c r="AM9" s="5" t="n"/>
+      <c r="AN9" s="5" t="n"/>
+      <c r="AO9" s="5" t="n"/>
+      <c r="AP9" s="5" t="n"/>
+      <c r="AQ9" s="5" t="n"/>
+      <c r="AR9" s="5" t="n"/>
+      <c r="AS9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -985,6 +1153,18 @@
       <c r="AE10" s="3" t="n"/>
       <c r="AF10" s="3" t="n"/>
       <c r="AG10" s="3" t="n"/>
+      <c r="AH10" s="3" t="n"/>
+      <c r="AI10" s="3" t="n"/>
+      <c r="AJ10" s="3" t="n"/>
+      <c r="AK10" s="3" t="n"/>
+      <c r="AL10" s="3" t="n"/>
+      <c r="AM10" s="3" t="n"/>
+      <c r="AN10" s="3" t="n"/>
+      <c r="AO10" s="3" t="n"/>
+      <c r="AP10" s="3" t="n"/>
+      <c r="AQ10" s="3" t="n"/>
+      <c r="AR10" s="3" t="n"/>
+      <c r="AS10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
@@ -1020,6 +1200,18 @@
       <c r="AE11" s="5" t="n"/>
       <c r="AF11" s="5" t="n"/>
       <c r="AG11" s="5" t="n"/>
+      <c r="AH11" s="5" t="n"/>
+      <c r="AI11" s="5" t="n"/>
+      <c r="AJ11" s="5" t="n"/>
+      <c r="AK11" s="5" t="n"/>
+      <c r="AL11" s="5" t="n"/>
+      <c r="AM11" s="5" t="n"/>
+      <c r="AN11" s="5" t="n"/>
+      <c r="AO11" s="5" t="n"/>
+      <c r="AP11" s="5" t="n"/>
+      <c r="AQ11" s="5" t="n"/>
+      <c r="AR11" s="5" t="n"/>
+      <c r="AS11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -1055,6 +1247,18 @@
       <c r="AE12" s="3" t="n"/>
       <c r="AF12" s="3" t="n"/>
       <c r="AG12" s="3" t="n"/>
+      <c r="AH12" s="3" t="n"/>
+      <c r="AI12" s="3" t="n"/>
+      <c r="AJ12" s="3" t="n"/>
+      <c r="AK12" s="3" t="n"/>
+      <c r="AL12" s="3" t="n"/>
+      <c r="AM12" s="3" t="n"/>
+      <c r="AN12" s="3" t="n"/>
+      <c r="AO12" s="3" t="n"/>
+      <c r="AP12" s="3" t="n"/>
+      <c r="AQ12" s="3" t="n"/>
+      <c r="AR12" s="3" t="n"/>
+      <c r="AS12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
@@ -1090,6 +1294,18 @@
       <c r="AE13" s="5" t="n"/>
       <c r="AF13" s="5" t="n"/>
       <c r="AG13" s="5" t="n"/>
+      <c r="AH13" s="5" t="n"/>
+      <c r="AI13" s="5" t="n"/>
+      <c r="AJ13" s="5" t="n"/>
+      <c r="AK13" s="5" t="n"/>
+      <c r="AL13" s="5" t="n"/>
+      <c r="AM13" s="5" t="n"/>
+      <c r="AN13" s="5" t="n"/>
+      <c r="AO13" s="5" t="n"/>
+      <c r="AP13" s="5" t="n"/>
+      <c r="AQ13" s="5" t="n"/>
+      <c r="AR13" s="5" t="n"/>
+      <c r="AS13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -1125,6 +1341,18 @@
       <c r="AE14" s="3" t="n"/>
       <c r="AF14" s="3" t="n"/>
       <c r="AG14" s="3" t="n"/>
+      <c r="AH14" s="3" t="n"/>
+      <c r="AI14" s="3" t="n"/>
+      <c r="AJ14" s="3" t="n"/>
+      <c r="AK14" s="3" t="n"/>
+      <c r="AL14" s="3" t="n"/>
+      <c r="AM14" s="3" t="n"/>
+      <c r="AN14" s="3" t="n"/>
+      <c r="AO14" s="3" t="n"/>
+      <c r="AP14" s="3" t="n"/>
+      <c r="AQ14" s="3" t="n"/>
+      <c r="AR14" s="3" t="n"/>
+      <c r="AS14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n"/>
@@ -1160,6 +1388,18 @@
       <c r="AE15" s="5" t="n"/>
       <c r="AF15" s="5" t="n"/>
       <c r="AG15" s="5" t="n"/>
+      <c r="AH15" s="5" t="n"/>
+      <c r="AI15" s="5" t="n"/>
+      <c r="AJ15" s="5" t="n"/>
+      <c r="AK15" s="5" t="n"/>
+      <c r="AL15" s="5" t="n"/>
+      <c r="AM15" s="5" t="n"/>
+      <c r="AN15" s="5" t="n"/>
+      <c r="AO15" s="5" t="n"/>
+      <c r="AP15" s="5" t="n"/>
+      <c r="AQ15" s="5" t="n"/>
+      <c r="AR15" s="5" t="n"/>
+      <c r="AS15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1195,6 +1435,18 @@
       <c r="AE16" s="3" t="n"/>
       <c r="AF16" s="3" t="n"/>
       <c r="AG16" s="3" t="n"/>
+      <c r="AH16" s="3" t="n"/>
+      <c r="AI16" s="3" t="n"/>
+      <c r="AJ16" s="3" t="n"/>
+      <c r="AK16" s="3" t="n"/>
+      <c r="AL16" s="3" t="n"/>
+      <c r="AM16" s="3" t="n"/>
+      <c r="AN16" s="3" t="n"/>
+      <c r="AO16" s="3" t="n"/>
+      <c r="AP16" s="3" t="n"/>
+      <c r="AQ16" s="3" t="n"/>
+      <c r="AR16" s="3" t="n"/>
+      <c r="AS16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
@@ -1230,6 +1482,18 @@
       <c r="AE17" s="5" t="n"/>
       <c r="AF17" s="5" t="n"/>
       <c r="AG17" s="5" t="n"/>
+      <c r="AH17" s="5" t="n"/>
+      <c r="AI17" s="5" t="n"/>
+      <c r="AJ17" s="5" t="n"/>
+      <c r="AK17" s="5" t="n"/>
+      <c r="AL17" s="5" t="n"/>
+      <c r="AM17" s="5" t="n"/>
+      <c r="AN17" s="5" t="n"/>
+      <c r="AO17" s="5" t="n"/>
+      <c r="AP17" s="5" t="n"/>
+      <c r="AQ17" s="5" t="n"/>
+      <c r="AR17" s="5" t="n"/>
+      <c r="AS17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1265,6 +1529,18 @@
       <c r="AE18" s="3" t="n"/>
       <c r="AF18" s="3" t="n"/>
       <c r="AG18" s="3" t="n"/>
+      <c r="AH18" s="3" t="n"/>
+      <c r="AI18" s="3" t="n"/>
+      <c r="AJ18" s="3" t="n"/>
+      <c r="AK18" s="3" t="n"/>
+      <c r="AL18" s="3" t="n"/>
+      <c r="AM18" s="3" t="n"/>
+      <c r="AN18" s="3" t="n"/>
+      <c r="AO18" s="3" t="n"/>
+      <c r="AP18" s="3" t="n"/>
+      <c r="AQ18" s="3" t="n"/>
+      <c r="AR18" s="3" t="n"/>
+      <c r="AS18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n"/>
@@ -1300,6 +1576,18 @@
       <c r="AE19" s="5" t="n"/>
       <c r="AF19" s="5" t="n"/>
       <c r="AG19" s="5" t="n"/>
+      <c r="AH19" s="5" t="n"/>
+      <c r="AI19" s="5" t="n"/>
+      <c r="AJ19" s="5" t="n"/>
+      <c r="AK19" s="5" t="n"/>
+      <c r="AL19" s="5" t="n"/>
+      <c r="AM19" s="5" t="n"/>
+      <c r="AN19" s="5" t="n"/>
+      <c r="AO19" s="5" t="n"/>
+      <c r="AP19" s="5" t="n"/>
+      <c r="AQ19" s="5" t="n"/>
+      <c r="AR19" s="5" t="n"/>
+      <c r="AS19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1335,6 +1623,18 @@
       <c r="AE20" s="3" t="n"/>
       <c r="AF20" s="3" t="n"/>
       <c r="AG20" s="3" t="n"/>
+      <c r="AH20" s="3" t="n"/>
+      <c r="AI20" s="3" t="n"/>
+      <c r="AJ20" s="3" t="n"/>
+      <c r="AK20" s="3" t="n"/>
+      <c r="AL20" s="3" t="n"/>
+      <c r="AM20" s="3" t="n"/>
+      <c r="AN20" s="3" t="n"/>
+      <c r="AO20" s="3" t="n"/>
+      <c r="AP20" s="3" t="n"/>
+      <c r="AQ20" s="3" t="n"/>
+      <c r="AR20" s="3" t="n"/>
+      <c r="AS20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n"/>
@@ -1370,6 +1670,18 @@
       <c r="AE21" s="5" t="n"/>
       <c r="AF21" s="5" t="n"/>
       <c r="AG21" s="5" t="n"/>
+      <c r="AH21" s="5" t="n"/>
+      <c r="AI21" s="5" t="n"/>
+      <c r="AJ21" s="5" t="n"/>
+      <c r="AK21" s="5" t="n"/>
+      <c r="AL21" s="5" t="n"/>
+      <c r="AM21" s="5" t="n"/>
+      <c r="AN21" s="5" t="n"/>
+      <c r="AO21" s="5" t="n"/>
+      <c r="AP21" s="5" t="n"/>
+      <c r="AQ21" s="5" t="n"/>
+      <c r="AR21" s="5" t="n"/>
+      <c r="AS21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -1405,6 +1717,18 @@
       <c r="AE22" s="3" t="n"/>
       <c r="AF22" s="3" t="n"/>
       <c r="AG22" s="3" t="n"/>
+      <c r="AH22" s="3" t="n"/>
+      <c r="AI22" s="3" t="n"/>
+      <c r="AJ22" s="3" t="n"/>
+      <c r="AK22" s="3" t="n"/>
+      <c r="AL22" s="3" t="n"/>
+      <c r="AM22" s="3" t="n"/>
+      <c r="AN22" s="3" t="n"/>
+      <c r="AO22" s="3" t="n"/>
+      <c r="AP22" s="3" t="n"/>
+      <c r="AQ22" s="3" t="n"/>
+      <c r="AR22" s="3" t="n"/>
+      <c r="AS22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n"/>
@@ -1440,6 +1764,18 @@
       <c r="AE23" s="5" t="n"/>
       <c r="AF23" s="5" t="n"/>
       <c r="AG23" s="5" t="n"/>
+      <c r="AH23" s="5" t="n"/>
+      <c r="AI23" s="5" t="n"/>
+      <c r="AJ23" s="5" t="n"/>
+      <c r="AK23" s="5" t="n"/>
+      <c r="AL23" s="5" t="n"/>
+      <c r="AM23" s="5" t="n"/>
+      <c r="AN23" s="5" t="n"/>
+      <c r="AO23" s="5" t="n"/>
+      <c r="AP23" s="5" t="n"/>
+      <c r="AQ23" s="5" t="n"/>
+      <c r="AR23" s="5" t="n"/>
+      <c r="AS23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1475,6 +1811,18 @@
       <c r="AE24" s="3" t="n"/>
       <c r="AF24" s="3" t="n"/>
       <c r="AG24" s="3" t="n"/>
+      <c r="AH24" s="3" t="n"/>
+      <c r="AI24" s="3" t="n"/>
+      <c r="AJ24" s="3" t="n"/>
+      <c r="AK24" s="3" t="n"/>
+      <c r="AL24" s="3" t="n"/>
+      <c r="AM24" s="3" t="n"/>
+      <c r="AN24" s="3" t="n"/>
+      <c r="AO24" s="3" t="n"/>
+      <c r="AP24" s="3" t="n"/>
+      <c r="AQ24" s="3" t="n"/>
+      <c r="AR24" s="3" t="n"/>
+      <c r="AS24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n"/>
@@ -1510,6 +1858,18 @@
       <c r="AE25" s="5" t="n"/>
       <c r="AF25" s="5" t="n"/>
       <c r="AG25" s="5" t="n"/>
+      <c r="AH25" s="5" t="n"/>
+      <c r="AI25" s="5" t="n"/>
+      <c r="AJ25" s="5" t="n"/>
+      <c r="AK25" s="5" t="n"/>
+      <c r="AL25" s="5" t="n"/>
+      <c r="AM25" s="5" t="n"/>
+      <c r="AN25" s="5" t="n"/>
+      <c r="AO25" s="5" t="n"/>
+      <c r="AP25" s="5" t="n"/>
+      <c r="AQ25" s="5" t="n"/>
+      <c r="AR25" s="5" t="n"/>
+      <c r="AS25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1545,6 +1905,18 @@
       <c r="AE26" s="3" t="n"/>
       <c r="AF26" s="3" t="n"/>
       <c r="AG26" s="3" t="n"/>
+      <c r="AH26" s="3" t="n"/>
+      <c r="AI26" s="3" t="n"/>
+      <c r="AJ26" s="3" t="n"/>
+      <c r="AK26" s="3" t="n"/>
+      <c r="AL26" s="3" t="n"/>
+      <c r="AM26" s="3" t="n"/>
+      <c r="AN26" s="3" t="n"/>
+      <c r="AO26" s="3" t="n"/>
+      <c r="AP26" s="3" t="n"/>
+      <c r="AQ26" s="3" t="n"/>
+      <c r="AR26" s="3" t="n"/>
+      <c r="AS26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n"/>
@@ -1580,6 +1952,18 @@
       <c r="AE27" s="5" t="n"/>
       <c r="AF27" s="5" t="n"/>
       <c r="AG27" s="5" t="n"/>
+      <c r="AH27" s="5" t="n"/>
+      <c r="AI27" s="5" t="n"/>
+      <c r="AJ27" s="5" t="n"/>
+      <c r="AK27" s="5" t="n"/>
+      <c r="AL27" s="5" t="n"/>
+      <c r="AM27" s="5" t="n"/>
+      <c r="AN27" s="5" t="n"/>
+      <c r="AO27" s="5" t="n"/>
+      <c r="AP27" s="5" t="n"/>
+      <c r="AQ27" s="5" t="n"/>
+      <c r="AR27" s="5" t="n"/>
+      <c r="AS27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -1615,6 +1999,18 @@
       <c r="AE28" s="3" t="n"/>
       <c r="AF28" s="3" t="n"/>
       <c r="AG28" s="3" t="n"/>
+      <c r="AH28" s="3" t="n"/>
+      <c r="AI28" s="3" t="n"/>
+      <c r="AJ28" s="3" t="n"/>
+      <c r="AK28" s="3" t="n"/>
+      <c r="AL28" s="3" t="n"/>
+      <c r="AM28" s="3" t="n"/>
+      <c r="AN28" s="3" t="n"/>
+      <c r="AO28" s="3" t="n"/>
+      <c r="AP28" s="3" t="n"/>
+      <c r="AQ28" s="3" t="n"/>
+      <c r="AR28" s="3" t="n"/>
+      <c r="AS28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n"/>
@@ -1650,6 +2046,18 @@
       <c r="AE29" s="5" t="n"/>
       <c r="AF29" s="5" t="n"/>
       <c r="AG29" s="5" t="n"/>
+      <c r="AH29" s="5" t="n"/>
+      <c r="AI29" s="5" t="n"/>
+      <c r="AJ29" s="5" t="n"/>
+      <c r="AK29" s="5" t="n"/>
+      <c r="AL29" s="5" t="n"/>
+      <c r="AM29" s="5" t="n"/>
+      <c r="AN29" s="5" t="n"/>
+      <c r="AO29" s="5" t="n"/>
+      <c r="AP29" s="5" t="n"/>
+      <c r="AQ29" s="5" t="n"/>
+      <c r="AR29" s="5" t="n"/>
+      <c r="AS29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -1685,6 +2093,18 @@
       <c r="AE30" s="3" t="n"/>
       <c r="AF30" s="3" t="n"/>
       <c r="AG30" s="3" t="n"/>
+      <c r="AH30" s="3" t="n"/>
+      <c r="AI30" s="3" t="n"/>
+      <c r="AJ30" s="3" t="n"/>
+      <c r="AK30" s="3" t="n"/>
+      <c r="AL30" s="3" t="n"/>
+      <c r="AM30" s="3" t="n"/>
+      <c r="AN30" s="3" t="n"/>
+      <c r="AO30" s="3" t="n"/>
+      <c r="AP30" s="3" t="n"/>
+      <c r="AQ30" s="3" t="n"/>
+      <c r="AR30" s="3" t="n"/>
+      <c r="AS30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n"/>
@@ -1720,6 +2140,18 @@
       <c r="AE31" s="5" t="n"/>
       <c r="AF31" s="5" t="n"/>
       <c r="AG31" s="5" t="n"/>
+      <c r="AH31" s="5" t="n"/>
+      <c r="AI31" s="5" t="n"/>
+      <c r="AJ31" s="5" t="n"/>
+      <c r="AK31" s="5" t="n"/>
+      <c r="AL31" s="5" t="n"/>
+      <c r="AM31" s="5" t="n"/>
+      <c r="AN31" s="5" t="n"/>
+      <c r="AO31" s="5" t="n"/>
+      <c r="AP31" s="5" t="n"/>
+      <c r="AQ31" s="5" t="n"/>
+      <c r="AR31" s="5" t="n"/>
+      <c r="AS31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -1755,6 +2187,18 @@
       <c r="AE32" s="3" t="n"/>
       <c r="AF32" s="3" t="n"/>
       <c r="AG32" s="3" t="n"/>
+      <c r="AH32" s="3" t="n"/>
+      <c r="AI32" s="3" t="n"/>
+      <c r="AJ32" s="3" t="n"/>
+      <c r="AK32" s="3" t="n"/>
+      <c r="AL32" s="3" t="n"/>
+      <c r="AM32" s="3" t="n"/>
+      <c r="AN32" s="3" t="n"/>
+      <c r="AO32" s="3" t="n"/>
+      <c r="AP32" s="3" t="n"/>
+      <c r="AQ32" s="3" t="n"/>
+      <c r="AR32" s="3" t="n"/>
+      <c r="AS32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n"/>
@@ -1790,6 +2234,18 @@
       <c r="AE33" s="5" t="n"/>
       <c r="AF33" s="5" t="n"/>
       <c r="AG33" s="5" t="n"/>
+      <c r="AH33" s="5" t="n"/>
+      <c r="AI33" s="5" t="n"/>
+      <c r="AJ33" s="5" t="n"/>
+      <c r="AK33" s="5" t="n"/>
+      <c r="AL33" s="5" t="n"/>
+      <c r="AM33" s="5" t="n"/>
+      <c r="AN33" s="5" t="n"/>
+      <c r="AO33" s="5" t="n"/>
+      <c r="AP33" s="5" t="n"/>
+      <c r="AQ33" s="5" t="n"/>
+      <c r="AR33" s="5" t="n"/>
+      <c r="AS33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -1825,6 +2281,18 @@
       <c r="AE34" s="3" t="n"/>
       <c r="AF34" s="3" t="n"/>
       <c r="AG34" s="3" t="n"/>
+      <c r="AH34" s="3" t="n"/>
+      <c r="AI34" s="3" t="n"/>
+      <c r="AJ34" s="3" t="n"/>
+      <c r="AK34" s="3" t="n"/>
+      <c r="AL34" s="3" t="n"/>
+      <c r="AM34" s="3" t="n"/>
+      <c r="AN34" s="3" t="n"/>
+      <c r="AO34" s="3" t="n"/>
+      <c r="AP34" s="3" t="n"/>
+      <c r="AQ34" s="3" t="n"/>
+      <c r="AR34" s="3" t="n"/>
+      <c r="AS34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n"/>
@@ -1860,6 +2328,18 @@
       <c r="AE35" s="5" t="n"/>
       <c r="AF35" s="5" t="n"/>
       <c r="AG35" s="5" t="n"/>
+      <c r="AH35" s="5" t="n"/>
+      <c r="AI35" s="5" t="n"/>
+      <c r="AJ35" s="5" t="n"/>
+      <c r="AK35" s="5" t="n"/>
+      <c r="AL35" s="5" t="n"/>
+      <c r="AM35" s="5" t="n"/>
+      <c r="AN35" s="5" t="n"/>
+      <c r="AO35" s="5" t="n"/>
+      <c r="AP35" s="5" t="n"/>
+      <c r="AQ35" s="5" t="n"/>
+      <c r="AR35" s="5" t="n"/>
+      <c r="AS35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -1895,6 +2375,18 @@
       <c r="AE36" s="3" t="n"/>
       <c r="AF36" s="3" t="n"/>
       <c r="AG36" s="3" t="n"/>
+      <c r="AH36" s="3" t="n"/>
+      <c r="AI36" s="3" t="n"/>
+      <c r="AJ36" s="3" t="n"/>
+      <c r="AK36" s="3" t="n"/>
+      <c r="AL36" s="3" t="n"/>
+      <c r="AM36" s="3" t="n"/>
+      <c r="AN36" s="3" t="n"/>
+      <c r="AO36" s="3" t="n"/>
+      <c r="AP36" s="3" t="n"/>
+      <c r="AQ36" s="3" t="n"/>
+      <c r="AR36" s="3" t="n"/>
+      <c r="AS36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n"/>
@@ -1930,6 +2422,18 @@
       <c r="AE37" s="5" t="n"/>
       <c r="AF37" s="5" t="n"/>
       <c r="AG37" s="5" t="n"/>
+      <c r="AH37" s="5" t="n"/>
+      <c r="AI37" s="5" t="n"/>
+      <c r="AJ37" s="5" t="n"/>
+      <c r="AK37" s="5" t="n"/>
+      <c r="AL37" s="5" t="n"/>
+      <c r="AM37" s="5" t="n"/>
+      <c r="AN37" s="5" t="n"/>
+      <c r="AO37" s="5" t="n"/>
+      <c r="AP37" s="5" t="n"/>
+      <c r="AQ37" s="5" t="n"/>
+      <c r="AR37" s="5" t="n"/>
+      <c r="AS37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -1965,6 +2469,18 @@
       <c r="AE38" s="3" t="n"/>
       <c r="AF38" s="3" t="n"/>
       <c r="AG38" s="3" t="n"/>
+      <c r="AH38" s="3" t="n"/>
+      <c r="AI38" s="3" t="n"/>
+      <c r="AJ38" s="3" t="n"/>
+      <c r="AK38" s="3" t="n"/>
+      <c r="AL38" s="3" t="n"/>
+      <c r="AM38" s="3" t="n"/>
+      <c r="AN38" s="3" t="n"/>
+      <c r="AO38" s="3" t="n"/>
+      <c r="AP38" s="3" t="n"/>
+      <c r="AQ38" s="3" t="n"/>
+      <c r="AR38" s="3" t="n"/>
+      <c r="AS38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n"/>
@@ -2000,6 +2516,18 @@
       <c r="AE39" s="5" t="n"/>
       <c r="AF39" s="5" t="n"/>
       <c r="AG39" s="5" t="n"/>
+      <c r="AH39" s="5" t="n"/>
+      <c r="AI39" s="5" t="n"/>
+      <c r="AJ39" s="5" t="n"/>
+      <c r="AK39" s="5" t="n"/>
+      <c r="AL39" s="5" t="n"/>
+      <c r="AM39" s="5" t="n"/>
+      <c r="AN39" s="5" t="n"/>
+      <c r="AO39" s="5" t="n"/>
+      <c r="AP39" s="5" t="n"/>
+      <c r="AQ39" s="5" t="n"/>
+      <c r="AR39" s="5" t="n"/>
+      <c r="AS39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -2035,6 +2563,18 @@
       <c r="AE40" s="3" t="n"/>
       <c r="AF40" s="3" t="n"/>
       <c r="AG40" s="3" t="n"/>
+      <c r="AH40" s="3" t="n"/>
+      <c r="AI40" s="3" t="n"/>
+      <c r="AJ40" s="3" t="n"/>
+      <c r="AK40" s="3" t="n"/>
+      <c r="AL40" s="3" t="n"/>
+      <c r="AM40" s="3" t="n"/>
+      <c r="AN40" s="3" t="n"/>
+      <c r="AO40" s="3" t="n"/>
+      <c r="AP40" s="3" t="n"/>
+      <c r="AQ40" s="3" t="n"/>
+      <c r="AR40" s="3" t="n"/>
+      <c r="AS40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n"/>
@@ -2070,6 +2610,18 @@
       <c r="AE41" s="5" t="n"/>
       <c r="AF41" s="5" t="n"/>
       <c r="AG41" s="5" t="n"/>
+      <c r="AH41" s="5" t="n"/>
+      <c r="AI41" s="5" t="n"/>
+      <c r="AJ41" s="5" t="n"/>
+      <c r="AK41" s="5" t="n"/>
+      <c r="AL41" s="5" t="n"/>
+      <c r="AM41" s="5" t="n"/>
+      <c r="AN41" s="5" t="n"/>
+      <c r="AO41" s="5" t="n"/>
+      <c r="AP41" s="5" t="n"/>
+      <c r="AQ41" s="5" t="n"/>
+      <c r="AR41" s="5" t="n"/>
+      <c r="AS41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -2105,6 +2657,18 @@
       <c r="AE42" s="3" t="n"/>
       <c r="AF42" s="3" t="n"/>
       <c r="AG42" s="3" t="n"/>
+      <c r="AH42" s="3" t="n"/>
+      <c r="AI42" s="3" t="n"/>
+      <c r="AJ42" s="3" t="n"/>
+      <c r="AK42" s="3" t="n"/>
+      <c r="AL42" s="3" t="n"/>
+      <c r="AM42" s="3" t="n"/>
+      <c r="AN42" s="3" t="n"/>
+      <c r="AO42" s="3" t="n"/>
+      <c r="AP42" s="3" t="n"/>
+      <c r="AQ42" s="3" t="n"/>
+      <c r="AR42" s="3" t="n"/>
+      <c r="AS42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
@@ -2140,6 +2704,18 @@
       <c r="AE43" s="5" t="n"/>
       <c r="AF43" s="5" t="n"/>
       <c r="AG43" s="5" t="n"/>
+      <c r="AH43" s="5" t="n"/>
+      <c r="AI43" s="5" t="n"/>
+      <c r="AJ43" s="5" t="n"/>
+      <c r="AK43" s="5" t="n"/>
+      <c r="AL43" s="5" t="n"/>
+      <c r="AM43" s="5" t="n"/>
+      <c r="AN43" s="5" t="n"/>
+      <c r="AO43" s="5" t="n"/>
+      <c r="AP43" s="5" t="n"/>
+      <c r="AQ43" s="5" t="n"/>
+      <c r="AR43" s="5" t="n"/>
+      <c r="AS43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -2175,6 +2751,18 @@
       <c r="AE44" s="3" t="n"/>
       <c r="AF44" s="3" t="n"/>
       <c r="AG44" s="3" t="n"/>
+      <c r="AH44" s="3" t="n"/>
+      <c r="AI44" s="3" t="n"/>
+      <c r="AJ44" s="3" t="n"/>
+      <c r="AK44" s="3" t="n"/>
+      <c r="AL44" s="3" t="n"/>
+      <c r="AM44" s="3" t="n"/>
+      <c r="AN44" s="3" t="n"/>
+      <c r="AO44" s="3" t="n"/>
+      <c r="AP44" s="3" t="n"/>
+      <c r="AQ44" s="3" t="n"/>
+      <c r="AR44" s="3" t="n"/>
+      <c r="AS44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n"/>
@@ -2210,6 +2798,18 @@
       <c r="AE45" s="5" t="n"/>
       <c r="AF45" s="5" t="n"/>
       <c r="AG45" s="5" t="n"/>
+      <c r="AH45" s="5" t="n"/>
+      <c r="AI45" s="5" t="n"/>
+      <c r="AJ45" s="5" t="n"/>
+      <c r="AK45" s="5" t="n"/>
+      <c r="AL45" s="5" t="n"/>
+      <c r="AM45" s="5" t="n"/>
+      <c r="AN45" s="5" t="n"/>
+      <c r="AO45" s="5" t="n"/>
+      <c r="AP45" s="5" t="n"/>
+      <c r="AQ45" s="5" t="n"/>
+      <c r="AR45" s="5" t="n"/>
+      <c r="AS45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -2245,6 +2845,18 @@
       <c r="AE46" s="3" t="n"/>
       <c r="AF46" s="3" t="n"/>
       <c r="AG46" s="3" t="n"/>
+      <c r="AH46" s="3" t="n"/>
+      <c r="AI46" s="3" t="n"/>
+      <c r="AJ46" s="3" t="n"/>
+      <c r="AK46" s="3" t="n"/>
+      <c r="AL46" s="3" t="n"/>
+      <c r="AM46" s="3" t="n"/>
+      <c r="AN46" s="3" t="n"/>
+      <c r="AO46" s="3" t="n"/>
+      <c r="AP46" s="3" t="n"/>
+      <c r="AQ46" s="3" t="n"/>
+      <c r="AR46" s="3" t="n"/>
+      <c r="AS46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n"/>
@@ -2280,6 +2892,18 @@
       <c r="AE47" s="5" t="n"/>
       <c r="AF47" s="5" t="n"/>
       <c r="AG47" s="5" t="n"/>
+      <c r="AH47" s="5" t="n"/>
+      <c r="AI47" s="5" t="n"/>
+      <c r="AJ47" s="5" t="n"/>
+      <c r="AK47" s="5" t="n"/>
+      <c r="AL47" s="5" t="n"/>
+      <c r="AM47" s="5" t="n"/>
+      <c r="AN47" s="5" t="n"/>
+      <c r="AO47" s="5" t="n"/>
+      <c r="AP47" s="5" t="n"/>
+      <c r="AQ47" s="5" t="n"/>
+      <c r="AR47" s="5" t="n"/>
+      <c r="AS47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -2315,6 +2939,18 @@
       <c r="AE48" s="3" t="n"/>
       <c r="AF48" s="3" t="n"/>
       <c r="AG48" s="3" t="n"/>
+      <c r="AH48" s="3" t="n"/>
+      <c r="AI48" s="3" t="n"/>
+      <c r="AJ48" s="3" t="n"/>
+      <c r="AK48" s="3" t="n"/>
+      <c r="AL48" s="3" t="n"/>
+      <c r="AM48" s="3" t="n"/>
+      <c r="AN48" s="3" t="n"/>
+      <c r="AO48" s="3" t="n"/>
+      <c r="AP48" s="3" t="n"/>
+      <c r="AQ48" s="3" t="n"/>
+      <c r="AR48" s="3" t="n"/>
+      <c r="AS48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n"/>
@@ -2350,6 +2986,18 @@
       <c r="AE49" s="5" t="n"/>
       <c r="AF49" s="5" t="n"/>
       <c r="AG49" s="5" t="n"/>
+      <c r="AH49" s="5" t="n"/>
+      <c r="AI49" s="5" t="n"/>
+      <c r="AJ49" s="5" t="n"/>
+      <c r="AK49" s="5" t="n"/>
+      <c r="AL49" s="5" t="n"/>
+      <c r="AM49" s="5" t="n"/>
+      <c r="AN49" s="5" t="n"/>
+      <c r="AO49" s="5" t="n"/>
+      <c r="AP49" s="5" t="n"/>
+      <c r="AQ49" s="5" t="n"/>
+      <c r="AR49" s="5" t="n"/>
+      <c r="AS49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -2385,6 +3033,18 @@
       <c r="AE50" s="3" t="n"/>
       <c r="AF50" s="3" t="n"/>
       <c r="AG50" s="3" t="n"/>
+      <c r="AH50" s="3" t="n"/>
+      <c r="AI50" s="3" t="n"/>
+      <c r="AJ50" s="3" t="n"/>
+      <c r="AK50" s="3" t="n"/>
+      <c r="AL50" s="3" t="n"/>
+      <c r="AM50" s="3" t="n"/>
+      <c r="AN50" s="3" t="n"/>
+      <c r="AO50" s="3" t="n"/>
+      <c r="AP50" s="3" t="n"/>
+      <c r="AQ50" s="3" t="n"/>
+      <c r="AR50" s="3" t="n"/>
+      <c r="AS50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n"/>
@@ -2420,6 +3080,18 @@
       <c r="AE51" s="5" t="n"/>
       <c r="AF51" s="5" t="n"/>
       <c r="AG51" s="5" t="n"/>
+      <c r="AH51" s="5" t="n"/>
+      <c r="AI51" s="5" t="n"/>
+      <c r="AJ51" s="5" t="n"/>
+      <c r="AK51" s="5" t="n"/>
+      <c r="AL51" s="5" t="n"/>
+      <c r="AM51" s="5" t="n"/>
+      <c r="AN51" s="5" t="n"/>
+      <c r="AO51" s="5" t="n"/>
+      <c r="AP51" s="5" t="n"/>
+      <c r="AQ51" s="5" t="n"/>
+      <c r="AR51" s="5" t="n"/>
+      <c r="AS51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -2455,6 +3127,18 @@
       <c r="AE52" s="3" t="n"/>
       <c r="AF52" s="3" t="n"/>
       <c r="AG52" s="3" t="n"/>
+      <c r="AH52" s="3" t="n"/>
+      <c r="AI52" s="3" t="n"/>
+      <c r="AJ52" s="3" t="n"/>
+      <c r="AK52" s="3" t="n"/>
+      <c r="AL52" s="3" t="n"/>
+      <c r="AM52" s="3" t="n"/>
+      <c r="AN52" s="3" t="n"/>
+      <c r="AO52" s="3" t="n"/>
+      <c r="AP52" s="3" t="n"/>
+      <c r="AQ52" s="3" t="n"/>
+      <c r="AR52" s="3" t="n"/>
+      <c r="AS52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n"/>
@@ -2490,6 +3174,18 @@
       <c r="AE53" s="5" t="n"/>
       <c r="AF53" s="5" t="n"/>
       <c r="AG53" s="5" t="n"/>
+      <c r="AH53" s="5" t="n"/>
+      <c r="AI53" s="5" t="n"/>
+      <c r="AJ53" s="5" t="n"/>
+      <c r="AK53" s="5" t="n"/>
+      <c r="AL53" s="5" t="n"/>
+      <c r="AM53" s="5" t="n"/>
+      <c r="AN53" s="5" t="n"/>
+      <c r="AO53" s="5" t="n"/>
+      <c r="AP53" s="5" t="n"/>
+      <c r="AQ53" s="5" t="n"/>
+      <c r="AR53" s="5" t="n"/>
+      <c r="AS53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -2525,6 +3221,18 @@
       <c r="AE54" s="3" t="n"/>
       <c r="AF54" s="3" t="n"/>
       <c r="AG54" s="3" t="n"/>
+      <c r="AH54" s="3" t="n"/>
+      <c r="AI54" s="3" t="n"/>
+      <c r="AJ54" s="3" t="n"/>
+      <c r="AK54" s="3" t="n"/>
+      <c r="AL54" s="3" t="n"/>
+      <c r="AM54" s="3" t="n"/>
+      <c r="AN54" s="3" t="n"/>
+      <c r="AO54" s="3" t="n"/>
+      <c r="AP54" s="3" t="n"/>
+      <c r="AQ54" s="3" t="n"/>
+      <c r="AR54" s="3" t="n"/>
+      <c r="AS54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n"/>
@@ -2560,6 +3268,18 @@
       <c r="AE55" s="5" t="n"/>
       <c r="AF55" s="5" t="n"/>
       <c r="AG55" s="5" t="n"/>
+      <c r="AH55" s="5" t="n"/>
+      <c r="AI55" s="5" t="n"/>
+      <c r="AJ55" s="5" t="n"/>
+      <c r="AK55" s="5" t="n"/>
+      <c r="AL55" s="5" t="n"/>
+      <c r="AM55" s="5" t="n"/>
+      <c r="AN55" s="5" t="n"/>
+      <c r="AO55" s="5" t="n"/>
+      <c r="AP55" s="5" t="n"/>
+      <c r="AQ55" s="5" t="n"/>
+      <c r="AR55" s="5" t="n"/>
+      <c r="AS55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -2595,6 +3315,18 @@
       <c r="AE56" s="3" t="n"/>
       <c r="AF56" s="3" t="n"/>
       <c r="AG56" s="3" t="n"/>
+      <c r="AH56" s="3" t="n"/>
+      <c r="AI56" s="3" t="n"/>
+      <c r="AJ56" s="3" t="n"/>
+      <c r="AK56" s="3" t="n"/>
+      <c r="AL56" s="3" t="n"/>
+      <c r="AM56" s="3" t="n"/>
+      <c r="AN56" s="3" t="n"/>
+      <c r="AO56" s="3" t="n"/>
+      <c r="AP56" s="3" t="n"/>
+      <c r="AQ56" s="3" t="n"/>
+      <c r="AR56" s="3" t="n"/>
+      <c r="AS56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n"/>
@@ -2630,6 +3362,18 @@
       <c r="AE57" s="5" t="n"/>
       <c r="AF57" s="5" t="n"/>
       <c r="AG57" s="5" t="n"/>
+      <c r="AH57" s="5" t="n"/>
+      <c r="AI57" s="5" t="n"/>
+      <c r="AJ57" s="5" t="n"/>
+      <c r="AK57" s="5" t="n"/>
+      <c r="AL57" s="5" t="n"/>
+      <c r="AM57" s="5" t="n"/>
+      <c r="AN57" s="5" t="n"/>
+      <c r="AO57" s="5" t="n"/>
+      <c r="AP57" s="5" t="n"/>
+      <c r="AQ57" s="5" t="n"/>
+      <c r="AR57" s="5" t="n"/>
+      <c r="AS57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -2665,6 +3409,18 @@
       <c r="AE58" s="3" t="n"/>
       <c r="AF58" s="3" t="n"/>
       <c r="AG58" s="3" t="n"/>
+      <c r="AH58" s="3" t="n"/>
+      <c r="AI58" s="3" t="n"/>
+      <c r="AJ58" s="3" t="n"/>
+      <c r="AK58" s="3" t="n"/>
+      <c r="AL58" s="3" t="n"/>
+      <c r="AM58" s="3" t="n"/>
+      <c r="AN58" s="3" t="n"/>
+      <c r="AO58" s="3" t="n"/>
+      <c r="AP58" s="3" t="n"/>
+      <c r="AQ58" s="3" t="n"/>
+      <c r="AR58" s="3" t="n"/>
+      <c r="AS58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n"/>
@@ -2700,6 +3456,18 @@
       <c r="AE59" s="5" t="n"/>
       <c r="AF59" s="5" t="n"/>
       <c r="AG59" s="5" t="n"/>
+      <c r="AH59" s="5" t="n"/>
+      <c r="AI59" s="5" t="n"/>
+      <c r="AJ59" s="5" t="n"/>
+      <c r="AK59" s="5" t="n"/>
+      <c r="AL59" s="5" t="n"/>
+      <c r="AM59" s="5" t="n"/>
+      <c r="AN59" s="5" t="n"/>
+      <c r="AO59" s="5" t="n"/>
+      <c r="AP59" s="5" t="n"/>
+      <c r="AQ59" s="5" t="n"/>
+      <c r="AR59" s="5" t="n"/>
+      <c r="AS59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -2735,6 +3503,18 @@
       <c r="AE60" s="3" t="n"/>
       <c r="AF60" s="3" t="n"/>
       <c r="AG60" s="3" t="n"/>
+      <c r="AH60" s="3" t="n"/>
+      <c r="AI60" s="3" t="n"/>
+      <c r="AJ60" s="3" t="n"/>
+      <c r="AK60" s="3" t="n"/>
+      <c r="AL60" s="3" t="n"/>
+      <c r="AM60" s="3" t="n"/>
+      <c r="AN60" s="3" t="n"/>
+      <c r="AO60" s="3" t="n"/>
+      <c r="AP60" s="3" t="n"/>
+      <c r="AQ60" s="3" t="n"/>
+      <c r="AR60" s="3" t="n"/>
+      <c r="AS60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n"/>
@@ -2770,6 +3550,18 @@
       <c r="AE61" s="5" t="n"/>
       <c r="AF61" s="5" t="n"/>
       <c r="AG61" s="5" t="n"/>
+      <c r="AH61" s="5" t="n"/>
+      <c r="AI61" s="5" t="n"/>
+      <c r="AJ61" s="5" t="n"/>
+      <c r="AK61" s="5" t="n"/>
+      <c r="AL61" s="5" t="n"/>
+      <c r="AM61" s="5" t="n"/>
+      <c r="AN61" s="5" t="n"/>
+      <c r="AO61" s="5" t="n"/>
+      <c r="AP61" s="5" t="n"/>
+      <c r="AQ61" s="5" t="n"/>
+      <c r="AR61" s="5" t="n"/>
+      <c r="AS61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
@@ -2805,6 +3597,18 @@
       <c r="AE62" s="3" t="n"/>
       <c r="AF62" s="3" t="n"/>
       <c r="AG62" s="3" t="n"/>
+      <c r="AH62" s="3" t="n"/>
+      <c r="AI62" s="3" t="n"/>
+      <c r="AJ62" s="3" t="n"/>
+      <c r="AK62" s="3" t="n"/>
+      <c r="AL62" s="3" t="n"/>
+      <c r="AM62" s="3" t="n"/>
+      <c r="AN62" s="3" t="n"/>
+      <c r="AO62" s="3" t="n"/>
+      <c r="AP62" s="3" t="n"/>
+      <c r="AQ62" s="3" t="n"/>
+      <c r="AR62" s="3" t="n"/>
+      <c r="AS62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n"/>
@@ -2840,6 +3644,18 @@
       <c r="AE63" s="5" t="n"/>
       <c r="AF63" s="5" t="n"/>
       <c r="AG63" s="5" t="n"/>
+      <c r="AH63" s="5" t="n"/>
+      <c r="AI63" s="5" t="n"/>
+      <c r="AJ63" s="5" t="n"/>
+      <c r="AK63" s="5" t="n"/>
+      <c r="AL63" s="5" t="n"/>
+      <c r="AM63" s="5" t="n"/>
+      <c r="AN63" s="5" t="n"/>
+      <c r="AO63" s="5" t="n"/>
+      <c r="AP63" s="5" t="n"/>
+      <c r="AQ63" s="5" t="n"/>
+      <c r="AR63" s="5" t="n"/>
+      <c r="AS63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
@@ -2875,6 +3691,18 @@
       <c r="AE64" s="3" t="n"/>
       <c r="AF64" s="3" t="n"/>
       <c r="AG64" s="3" t="n"/>
+      <c r="AH64" s="3" t="n"/>
+      <c r="AI64" s="3" t="n"/>
+      <c r="AJ64" s="3" t="n"/>
+      <c r="AK64" s="3" t="n"/>
+      <c r="AL64" s="3" t="n"/>
+      <c r="AM64" s="3" t="n"/>
+      <c r="AN64" s="3" t="n"/>
+      <c r="AO64" s="3" t="n"/>
+      <c r="AP64" s="3" t="n"/>
+      <c r="AQ64" s="3" t="n"/>
+      <c r="AR64" s="3" t="n"/>
+      <c r="AS64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n"/>
@@ -2910,6 +3738,18 @@
       <c r="AE65" s="5" t="n"/>
       <c r="AF65" s="5" t="n"/>
       <c r="AG65" s="5" t="n"/>
+      <c r="AH65" s="5" t="n"/>
+      <c r="AI65" s="5" t="n"/>
+      <c r="AJ65" s="5" t="n"/>
+      <c r="AK65" s="5" t="n"/>
+      <c r="AL65" s="5" t="n"/>
+      <c r="AM65" s="5" t="n"/>
+      <c r="AN65" s="5" t="n"/>
+      <c r="AO65" s="5" t="n"/>
+      <c r="AP65" s="5" t="n"/>
+      <c r="AQ65" s="5" t="n"/>
+      <c r="AR65" s="5" t="n"/>
+      <c r="AS65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
@@ -2945,6 +3785,18 @@
       <c r="AE66" s="3" t="n"/>
       <c r="AF66" s="3" t="n"/>
       <c r="AG66" s="3" t="n"/>
+      <c r="AH66" s="3" t="n"/>
+      <c r="AI66" s="3" t="n"/>
+      <c r="AJ66" s="3" t="n"/>
+      <c r="AK66" s="3" t="n"/>
+      <c r="AL66" s="3" t="n"/>
+      <c r="AM66" s="3" t="n"/>
+      <c r="AN66" s="3" t="n"/>
+      <c r="AO66" s="3" t="n"/>
+      <c r="AP66" s="3" t="n"/>
+      <c r="AQ66" s="3" t="n"/>
+      <c r="AR66" s="3" t="n"/>
+      <c r="AS66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n"/>
@@ -2980,6 +3832,18 @@
       <c r="AE67" s="5" t="n"/>
       <c r="AF67" s="5" t="n"/>
       <c r="AG67" s="5" t="n"/>
+      <c r="AH67" s="5" t="n"/>
+      <c r="AI67" s="5" t="n"/>
+      <c r="AJ67" s="5" t="n"/>
+      <c r="AK67" s="5" t="n"/>
+      <c r="AL67" s="5" t="n"/>
+      <c r="AM67" s="5" t="n"/>
+      <c r="AN67" s="5" t="n"/>
+      <c r="AO67" s="5" t="n"/>
+      <c r="AP67" s="5" t="n"/>
+      <c r="AQ67" s="5" t="n"/>
+      <c r="AR67" s="5" t="n"/>
+      <c r="AS67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
@@ -3015,6 +3879,18 @@
       <c r="AE68" s="3" t="n"/>
       <c r="AF68" s="3" t="n"/>
       <c r="AG68" s="3" t="n"/>
+      <c r="AH68" s="3" t="n"/>
+      <c r="AI68" s="3" t="n"/>
+      <c r="AJ68" s="3" t="n"/>
+      <c r="AK68" s="3" t="n"/>
+      <c r="AL68" s="3" t="n"/>
+      <c r="AM68" s="3" t="n"/>
+      <c r="AN68" s="3" t="n"/>
+      <c r="AO68" s="3" t="n"/>
+      <c r="AP68" s="3" t="n"/>
+      <c r="AQ68" s="3" t="n"/>
+      <c r="AR68" s="3" t="n"/>
+      <c r="AS68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n"/>
@@ -3050,6 +3926,18 @@
       <c r="AE69" s="5" t="n"/>
       <c r="AF69" s="5" t="n"/>
       <c r="AG69" s="5" t="n"/>
+      <c r="AH69" s="5" t="n"/>
+      <c r="AI69" s="5" t="n"/>
+      <c r="AJ69" s="5" t="n"/>
+      <c r="AK69" s="5" t="n"/>
+      <c r="AL69" s="5" t="n"/>
+      <c r="AM69" s="5" t="n"/>
+      <c r="AN69" s="5" t="n"/>
+      <c r="AO69" s="5" t="n"/>
+      <c r="AP69" s="5" t="n"/>
+      <c r="AQ69" s="5" t="n"/>
+      <c r="AR69" s="5" t="n"/>
+      <c r="AS69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
@@ -3085,6 +3973,18 @@
       <c r="AE70" s="3" t="n"/>
       <c r="AF70" s="3" t="n"/>
       <c r="AG70" s="3" t="n"/>
+      <c r="AH70" s="3" t="n"/>
+      <c r="AI70" s="3" t="n"/>
+      <c r="AJ70" s="3" t="n"/>
+      <c r="AK70" s="3" t="n"/>
+      <c r="AL70" s="3" t="n"/>
+      <c r="AM70" s="3" t="n"/>
+      <c r="AN70" s="3" t="n"/>
+      <c r="AO70" s="3" t="n"/>
+      <c r="AP70" s="3" t="n"/>
+      <c r="AQ70" s="3" t="n"/>
+      <c r="AR70" s="3" t="n"/>
+      <c r="AS70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n"/>
@@ -3120,6 +4020,18 @@
       <c r="AE71" s="5" t="n"/>
       <c r="AF71" s="5" t="n"/>
       <c r="AG71" s="5" t="n"/>
+      <c r="AH71" s="5" t="n"/>
+      <c r="AI71" s="5" t="n"/>
+      <c r="AJ71" s="5" t="n"/>
+      <c r="AK71" s="5" t="n"/>
+      <c r="AL71" s="5" t="n"/>
+      <c r="AM71" s="5" t="n"/>
+      <c r="AN71" s="5" t="n"/>
+      <c r="AO71" s="5" t="n"/>
+      <c r="AP71" s="5" t="n"/>
+      <c r="AQ71" s="5" t="n"/>
+      <c r="AR71" s="5" t="n"/>
+      <c r="AS71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>
@@ -3155,6 +4067,18 @@
       <c r="AE72" s="3" t="n"/>
       <c r="AF72" s="3" t="n"/>
       <c r="AG72" s="3" t="n"/>
+      <c r="AH72" s="3" t="n"/>
+      <c r="AI72" s="3" t="n"/>
+      <c r="AJ72" s="3" t="n"/>
+      <c r="AK72" s="3" t="n"/>
+      <c r="AL72" s="3" t="n"/>
+      <c r="AM72" s="3" t="n"/>
+      <c r="AN72" s="3" t="n"/>
+      <c r="AO72" s="3" t="n"/>
+      <c r="AP72" s="3" t="n"/>
+      <c r="AQ72" s="3" t="n"/>
+      <c r="AR72" s="3" t="n"/>
+      <c r="AS72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n"/>
@@ -3190,6 +4114,18 @@
       <c r="AE73" s="5" t="n"/>
       <c r="AF73" s="5" t="n"/>
       <c r="AG73" s="5" t="n"/>
+      <c r="AH73" s="5" t="n"/>
+      <c r="AI73" s="5" t="n"/>
+      <c r="AJ73" s="5" t="n"/>
+      <c r="AK73" s="5" t="n"/>
+      <c r="AL73" s="5" t="n"/>
+      <c r="AM73" s="5" t="n"/>
+      <c r="AN73" s="5" t="n"/>
+      <c r="AO73" s="5" t="n"/>
+      <c r="AP73" s="5" t="n"/>
+      <c r="AQ73" s="5" t="n"/>
+      <c r="AR73" s="5" t="n"/>
+      <c r="AS73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
@@ -3225,6 +4161,18 @@
       <c r="AE74" s="3" t="n"/>
       <c r="AF74" s="3" t="n"/>
       <c r="AG74" s="3" t="n"/>
+      <c r="AH74" s="3" t="n"/>
+      <c r="AI74" s="3" t="n"/>
+      <c r="AJ74" s="3" t="n"/>
+      <c r="AK74" s="3" t="n"/>
+      <c r="AL74" s="3" t="n"/>
+      <c r="AM74" s="3" t="n"/>
+      <c r="AN74" s="3" t="n"/>
+      <c r="AO74" s="3" t="n"/>
+      <c r="AP74" s="3" t="n"/>
+      <c r="AQ74" s="3" t="n"/>
+      <c r="AR74" s="3" t="n"/>
+      <c r="AS74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n"/>
@@ -3260,6 +4208,18 @@
       <c r="AE75" s="5" t="n"/>
       <c r="AF75" s="5" t="n"/>
       <c r="AG75" s="5" t="n"/>
+      <c r="AH75" s="5" t="n"/>
+      <c r="AI75" s="5" t="n"/>
+      <c r="AJ75" s="5" t="n"/>
+      <c r="AK75" s="5" t="n"/>
+      <c r="AL75" s="5" t="n"/>
+      <c r="AM75" s="5" t="n"/>
+      <c r="AN75" s="5" t="n"/>
+      <c r="AO75" s="5" t="n"/>
+      <c r="AP75" s="5" t="n"/>
+      <c r="AQ75" s="5" t="n"/>
+      <c r="AR75" s="5" t="n"/>
+      <c r="AS75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>
@@ -3295,6 +4255,18 @@
       <c r="AE76" s="3" t="n"/>
       <c r="AF76" s="3" t="n"/>
       <c r="AG76" s="3" t="n"/>
+      <c r="AH76" s="3" t="n"/>
+      <c r="AI76" s="3" t="n"/>
+      <c r="AJ76" s="3" t="n"/>
+      <c r="AK76" s="3" t="n"/>
+      <c r="AL76" s="3" t="n"/>
+      <c r="AM76" s="3" t="n"/>
+      <c r="AN76" s="3" t="n"/>
+      <c r="AO76" s="3" t="n"/>
+      <c r="AP76" s="3" t="n"/>
+      <c r="AQ76" s="3" t="n"/>
+      <c r="AR76" s="3" t="n"/>
+      <c r="AS76" s="3" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n"/>
@@ -3330,6 +4302,18 @@
       <c r="AE77" s="5" t="n"/>
       <c r="AF77" s="5" t="n"/>
       <c r="AG77" s="5" t="n"/>
+      <c r="AH77" s="5" t="n"/>
+      <c r="AI77" s="5" t="n"/>
+      <c r="AJ77" s="5" t="n"/>
+      <c r="AK77" s="5" t="n"/>
+      <c r="AL77" s="5" t="n"/>
+      <c r="AM77" s="5" t="n"/>
+      <c r="AN77" s="5" t="n"/>
+      <c r="AO77" s="5" t="n"/>
+      <c r="AP77" s="5" t="n"/>
+      <c r="AQ77" s="5" t="n"/>
+      <c r="AR77" s="5" t="n"/>
+      <c r="AS77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
@@ -3365,6 +4349,18 @@
       <c r="AE78" s="3" t="n"/>
       <c r="AF78" s="3" t="n"/>
       <c r="AG78" s="3" t="n"/>
+      <c r="AH78" s="3" t="n"/>
+      <c r="AI78" s="3" t="n"/>
+      <c r="AJ78" s="3" t="n"/>
+      <c r="AK78" s="3" t="n"/>
+      <c r="AL78" s="3" t="n"/>
+      <c r="AM78" s="3" t="n"/>
+      <c r="AN78" s="3" t="n"/>
+      <c r="AO78" s="3" t="n"/>
+      <c r="AP78" s="3" t="n"/>
+      <c r="AQ78" s="3" t="n"/>
+      <c r="AR78" s="3" t="n"/>
+      <c r="AS78" s="3" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n"/>
@@ -3400,6 +4396,18 @@
       <c r="AE79" s="5" t="n"/>
       <c r="AF79" s="5" t="n"/>
       <c r="AG79" s="5" t="n"/>
+      <c r="AH79" s="5" t="n"/>
+      <c r="AI79" s="5" t="n"/>
+      <c r="AJ79" s="5" t="n"/>
+      <c r="AK79" s="5" t="n"/>
+      <c r="AL79" s="5" t="n"/>
+      <c r="AM79" s="5" t="n"/>
+      <c r="AN79" s="5" t="n"/>
+      <c r="AO79" s="5" t="n"/>
+      <c r="AP79" s="5" t="n"/>
+      <c r="AQ79" s="5" t="n"/>
+      <c r="AR79" s="5" t="n"/>
+      <c r="AS79" s="5" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
@@ -3435,6 +4443,18 @@
       <c r="AE80" s="3" t="n"/>
       <c r="AF80" s="3" t="n"/>
       <c r="AG80" s="3" t="n"/>
+      <c r="AH80" s="3" t="n"/>
+      <c r="AI80" s="3" t="n"/>
+      <c r="AJ80" s="3" t="n"/>
+      <c r="AK80" s="3" t="n"/>
+      <c r="AL80" s="3" t="n"/>
+      <c r="AM80" s="3" t="n"/>
+      <c r="AN80" s="3" t="n"/>
+      <c r="AO80" s="3" t="n"/>
+      <c r="AP80" s="3" t="n"/>
+      <c r="AQ80" s="3" t="n"/>
+      <c r="AR80" s="3" t="n"/>
+      <c r="AS80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n"/>
@@ -3470,6 +4490,18 @@
       <c r="AE81" s="5" t="n"/>
       <c r="AF81" s="5" t="n"/>
       <c r="AG81" s="5" t="n"/>
+      <c r="AH81" s="5" t="n"/>
+      <c r="AI81" s="5" t="n"/>
+      <c r="AJ81" s="5" t="n"/>
+      <c r="AK81" s="5" t="n"/>
+      <c r="AL81" s="5" t="n"/>
+      <c r="AM81" s="5" t="n"/>
+      <c r="AN81" s="5" t="n"/>
+      <c r="AO81" s="5" t="n"/>
+      <c r="AP81" s="5" t="n"/>
+      <c r="AQ81" s="5" t="n"/>
+      <c r="AR81" s="5" t="n"/>
+      <c r="AS81" s="5" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>
@@ -3505,6 +4537,18 @@
       <c r="AE82" s="3" t="n"/>
       <c r="AF82" s="3" t="n"/>
       <c r="AG82" s="3" t="n"/>
+      <c r="AH82" s="3" t="n"/>
+      <c r="AI82" s="3" t="n"/>
+      <c r="AJ82" s="3" t="n"/>
+      <c r="AK82" s="3" t="n"/>
+      <c r="AL82" s="3" t="n"/>
+      <c r="AM82" s="3" t="n"/>
+      <c r="AN82" s="3" t="n"/>
+      <c r="AO82" s="3" t="n"/>
+      <c r="AP82" s="3" t="n"/>
+      <c r="AQ82" s="3" t="n"/>
+      <c r="AR82" s="3" t="n"/>
+      <c r="AS82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n"/>
@@ -3540,6 +4584,18 @@
       <c r="AE83" s="5" t="n"/>
       <c r="AF83" s="5" t="n"/>
       <c r="AG83" s="5" t="n"/>
+      <c r="AH83" s="5" t="n"/>
+      <c r="AI83" s="5" t="n"/>
+      <c r="AJ83" s="5" t="n"/>
+      <c r="AK83" s="5" t="n"/>
+      <c r="AL83" s="5" t="n"/>
+      <c r="AM83" s="5" t="n"/>
+      <c r="AN83" s="5" t="n"/>
+      <c r="AO83" s="5" t="n"/>
+      <c r="AP83" s="5" t="n"/>
+      <c r="AQ83" s="5" t="n"/>
+      <c r="AR83" s="5" t="n"/>
+      <c r="AS83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
@@ -3575,6 +4631,18 @@
       <c r="AE84" s="3" t="n"/>
       <c r="AF84" s="3" t="n"/>
       <c r="AG84" s="3" t="n"/>
+      <c r="AH84" s="3" t="n"/>
+      <c r="AI84" s="3" t="n"/>
+      <c r="AJ84" s="3" t="n"/>
+      <c r="AK84" s="3" t="n"/>
+      <c r="AL84" s="3" t="n"/>
+      <c r="AM84" s="3" t="n"/>
+      <c r="AN84" s="3" t="n"/>
+      <c r="AO84" s="3" t="n"/>
+      <c r="AP84" s="3" t="n"/>
+      <c r="AQ84" s="3" t="n"/>
+      <c r="AR84" s="3" t="n"/>
+      <c r="AS84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n"/>
@@ -3610,6 +4678,18 @@
       <c r="AE85" s="5" t="n"/>
       <c r="AF85" s="5" t="n"/>
       <c r="AG85" s="5" t="n"/>
+      <c r="AH85" s="5" t="n"/>
+      <c r="AI85" s="5" t="n"/>
+      <c r="AJ85" s="5" t="n"/>
+      <c r="AK85" s="5" t="n"/>
+      <c r="AL85" s="5" t="n"/>
+      <c r="AM85" s="5" t="n"/>
+      <c r="AN85" s="5" t="n"/>
+      <c r="AO85" s="5" t="n"/>
+      <c r="AP85" s="5" t="n"/>
+      <c r="AQ85" s="5" t="n"/>
+      <c r="AR85" s="5" t="n"/>
+      <c r="AS85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>
@@ -3645,6 +4725,18 @@
       <c r="AE86" s="3" t="n"/>
       <c r="AF86" s="3" t="n"/>
       <c r="AG86" s="3" t="n"/>
+      <c r="AH86" s="3" t="n"/>
+      <c r="AI86" s="3" t="n"/>
+      <c r="AJ86" s="3" t="n"/>
+      <c r="AK86" s="3" t="n"/>
+      <c r="AL86" s="3" t="n"/>
+      <c r="AM86" s="3" t="n"/>
+      <c r="AN86" s="3" t="n"/>
+      <c r="AO86" s="3" t="n"/>
+      <c r="AP86" s="3" t="n"/>
+      <c r="AQ86" s="3" t="n"/>
+      <c r="AR86" s="3" t="n"/>
+      <c r="AS86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n"/>
@@ -3680,6 +4772,18 @@
       <c r="AE87" s="5" t="n"/>
       <c r="AF87" s="5" t="n"/>
       <c r="AG87" s="5" t="n"/>
+      <c r="AH87" s="5" t="n"/>
+      <c r="AI87" s="5" t="n"/>
+      <c r="AJ87" s="5" t="n"/>
+      <c r="AK87" s="5" t="n"/>
+      <c r="AL87" s="5" t="n"/>
+      <c r="AM87" s="5" t="n"/>
+      <c r="AN87" s="5" t="n"/>
+      <c r="AO87" s="5" t="n"/>
+      <c r="AP87" s="5" t="n"/>
+      <c r="AQ87" s="5" t="n"/>
+      <c r="AR87" s="5" t="n"/>
+      <c r="AS87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
@@ -3715,6 +4819,18 @@
       <c r="AE88" s="3" t="n"/>
       <c r="AF88" s="3" t="n"/>
       <c r="AG88" s="3" t="n"/>
+      <c r="AH88" s="3" t="n"/>
+      <c r="AI88" s="3" t="n"/>
+      <c r="AJ88" s="3" t="n"/>
+      <c r="AK88" s="3" t="n"/>
+      <c r="AL88" s="3" t="n"/>
+      <c r="AM88" s="3" t="n"/>
+      <c r="AN88" s="3" t="n"/>
+      <c r="AO88" s="3" t="n"/>
+      <c r="AP88" s="3" t="n"/>
+      <c r="AQ88" s="3" t="n"/>
+      <c r="AR88" s="3" t="n"/>
+      <c r="AS88" s="3" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n"/>
@@ -3750,6 +4866,18 @@
       <c r="AE89" s="5" t="n"/>
       <c r="AF89" s="5" t="n"/>
       <c r="AG89" s="5" t="n"/>
+      <c r="AH89" s="5" t="n"/>
+      <c r="AI89" s="5" t="n"/>
+      <c r="AJ89" s="5" t="n"/>
+      <c r="AK89" s="5" t="n"/>
+      <c r="AL89" s="5" t="n"/>
+      <c r="AM89" s="5" t="n"/>
+      <c r="AN89" s="5" t="n"/>
+      <c r="AO89" s="5" t="n"/>
+      <c r="AP89" s="5" t="n"/>
+      <c r="AQ89" s="5" t="n"/>
+      <c r="AR89" s="5" t="n"/>
+      <c r="AS89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>
@@ -3785,6 +4913,18 @@
       <c r="AE90" s="3" t="n"/>
       <c r="AF90" s="3" t="n"/>
       <c r="AG90" s="3" t="n"/>
+      <c r="AH90" s="3" t="n"/>
+      <c r="AI90" s="3" t="n"/>
+      <c r="AJ90" s="3" t="n"/>
+      <c r="AK90" s="3" t="n"/>
+      <c r="AL90" s="3" t="n"/>
+      <c r="AM90" s="3" t="n"/>
+      <c r="AN90" s="3" t="n"/>
+      <c r="AO90" s="3" t="n"/>
+      <c r="AP90" s="3" t="n"/>
+      <c r="AQ90" s="3" t="n"/>
+      <c r="AR90" s="3" t="n"/>
+      <c r="AS90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n"/>
@@ -3820,6 +4960,18 @@
       <c r="AE91" s="5" t="n"/>
       <c r="AF91" s="5" t="n"/>
       <c r="AG91" s="5" t="n"/>
+      <c r="AH91" s="5" t="n"/>
+      <c r="AI91" s="5" t="n"/>
+      <c r="AJ91" s="5" t="n"/>
+      <c r="AK91" s="5" t="n"/>
+      <c r="AL91" s="5" t="n"/>
+      <c r="AM91" s="5" t="n"/>
+      <c r="AN91" s="5" t="n"/>
+      <c r="AO91" s="5" t="n"/>
+      <c r="AP91" s="5" t="n"/>
+      <c r="AQ91" s="5" t="n"/>
+      <c r="AR91" s="5" t="n"/>
+      <c r="AS91" s="5" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
@@ -3855,6 +5007,18 @@
       <c r="AE92" s="3" t="n"/>
       <c r="AF92" s="3" t="n"/>
       <c r="AG92" s="3" t="n"/>
+      <c r="AH92" s="3" t="n"/>
+      <c r="AI92" s="3" t="n"/>
+      <c r="AJ92" s="3" t="n"/>
+      <c r="AK92" s="3" t="n"/>
+      <c r="AL92" s="3" t="n"/>
+      <c r="AM92" s="3" t="n"/>
+      <c r="AN92" s="3" t="n"/>
+      <c r="AO92" s="3" t="n"/>
+      <c r="AP92" s="3" t="n"/>
+      <c r="AQ92" s="3" t="n"/>
+      <c r="AR92" s="3" t="n"/>
+      <c r="AS92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n"/>
@@ -3890,6 +5054,18 @@
       <c r="AE93" s="5" t="n"/>
       <c r="AF93" s="5" t="n"/>
       <c r="AG93" s="5" t="n"/>
+      <c r="AH93" s="5" t="n"/>
+      <c r="AI93" s="5" t="n"/>
+      <c r="AJ93" s="5" t="n"/>
+      <c r="AK93" s="5" t="n"/>
+      <c r="AL93" s="5" t="n"/>
+      <c r="AM93" s="5" t="n"/>
+      <c r="AN93" s="5" t="n"/>
+      <c r="AO93" s="5" t="n"/>
+      <c r="AP93" s="5" t="n"/>
+      <c r="AQ93" s="5" t="n"/>
+      <c r="AR93" s="5" t="n"/>
+      <c r="AS93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>
@@ -3925,6 +5101,18 @@
       <c r="AE94" s="3" t="n"/>
       <c r="AF94" s="3" t="n"/>
       <c r="AG94" s="3" t="n"/>
+      <c r="AH94" s="3" t="n"/>
+      <c r="AI94" s="3" t="n"/>
+      <c r="AJ94" s="3" t="n"/>
+      <c r="AK94" s="3" t="n"/>
+      <c r="AL94" s="3" t="n"/>
+      <c r="AM94" s="3" t="n"/>
+      <c r="AN94" s="3" t="n"/>
+      <c r="AO94" s="3" t="n"/>
+      <c r="AP94" s="3" t="n"/>
+      <c r="AQ94" s="3" t="n"/>
+      <c r="AR94" s="3" t="n"/>
+      <c r="AS94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n"/>
@@ -3960,6 +5148,18 @@
       <c r="AE95" s="5" t="n"/>
       <c r="AF95" s="5" t="n"/>
       <c r="AG95" s="5" t="n"/>
+      <c r="AH95" s="5" t="n"/>
+      <c r="AI95" s="5" t="n"/>
+      <c r="AJ95" s="5" t="n"/>
+      <c r="AK95" s="5" t="n"/>
+      <c r="AL95" s="5" t="n"/>
+      <c r="AM95" s="5" t="n"/>
+      <c r="AN95" s="5" t="n"/>
+      <c r="AO95" s="5" t="n"/>
+      <c r="AP95" s="5" t="n"/>
+      <c r="AQ95" s="5" t="n"/>
+      <c r="AR95" s="5" t="n"/>
+      <c r="AS95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>
@@ -3995,6 +5195,18 @@
       <c r="AE96" s="3" t="n"/>
       <c r="AF96" s="3" t="n"/>
       <c r="AG96" s="3" t="n"/>
+      <c r="AH96" s="3" t="n"/>
+      <c r="AI96" s="3" t="n"/>
+      <c r="AJ96" s="3" t="n"/>
+      <c r="AK96" s="3" t="n"/>
+      <c r="AL96" s="3" t="n"/>
+      <c r="AM96" s="3" t="n"/>
+      <c r="AN96" s="3" t="n"/>
+      <c r="AO96" s="3" t="n"/>
+      <c r="AP96" s="3" t="n"/>
+      <c r="AQ96" s="3" t="n"/>
+      <c r="AR96" s="3" t="n"/>
+      <c r="AS96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n"/>
@@ -4030,6 +5242,18 @@
       <c r="AE97" s="5" t="n"/>
       <c r="AF97" s="5" t="n"/>
       <c r="AG97" s="5" t="n"/>
+      <c r="AH97" s="5" t="n"/>
+      <c r="AI97" s="5" t="n"/>
+      <c r="AJ97" s="5" t="n"/>
+      <c r="AK97" s="5" t="n"/>
+      <c r="AL97" s="5" t="n"/>
+      <c r="AM97" s="5" t="n"/>
+      <c r="AN97" s="5" t="n"/>
+      <c r="AO97" s="5" t="n"/>
+      <c r="AP97" s="5" t="n"/>
+      <c r="AQ97" s="5" t="n"/>
+      <c r="AR97" s="5" t="n"/>
+      <c r="AS97" s="5" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
@@ -4065,6 +5289,18 @@
       <c r="AE98" s="3" t="n"/>
       <c r="AF98" s="3" t="n"/>
       <c r="AG98" s="3" t="n"/>
+      <c r="AH98" s="3" t="n"/>
+      <c r="AI98" s="3" t="n"/>
+      <c r="AJ98" s="3" t="n"/>
+      <c r="AK98" s="3" t="n"/>
+      <c r="AL98" s="3" t="n"/>
+      <c r="AM98" s="3" t="n"/>
+      <c r="AN98" s="3" t="n"/>
+      <c r="AO98" s="3" t="n"/>
+      <c r="AP98" s="3" t="n"/>
+      <c r="AQ98" s="3" t="n"/>
+      <c r="AR98" s="3" t="n"/>
+      <c r="AS98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n"/>
@@ -4100,6 +5336,18 @@
       <c r="AE99" s="5" t="n"/>
       <c r="AF99" s="5" t="n"/>
       <c r="AG99" s="5" t="n"/>
+      <c r="AH99" s="5" t="n"/>
+      <c r="AI99" s="5" t="n"/>
+      <c r="AJ99" s="5" t="n"/>
+      <c r="AK99" s="5" t="n"/>
+      <c r="AL99" s="5" t="n"/>
+      <c r="AM99" s="5" t="n"/>
+      <c r="AN99" s="5" t="n"/>
+      <c r="AO99" s="5" t="n"/>
+      <c r="AP99" s="5" t="n"/>
+      <c r="AQ99" s="5" t="n"/>
+      <c r="AR99" s="5" t="n"/>
+      <c r="AS99" s="5" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n"/>
@@ -4135,6 +5383,18 @@
       <c r="AE100" s="3" t="n"/>
       <c r="AF100" s="3" t="n"/>
       <c r="AG100" s="3" t="n"/>
+      <c r="AH100" s="3" t="n"/>
+      <c r="AI100" s="3" t="n"/>
+      <c r="AJ100" s="3" t="n"/>
+      <c r="AK100" s="3" t="n"/>
+      <c r="AL100" s="3" t="n"/>
+      <c r="AM100" s="3" t="n"/>
+      <c r="AN100" s="3" t="n"/>
+      <c r="AO100" s="3" t="n"/>
+      <c r="AP100" s="3" t="n"/>
+      <c r="AQ100" s="3" t="n"/>
+      <c r="AR100" s="3" t="n"/>
+      <c r="AS100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n"/>
@@ -4170,6 +5430,18 @@
       <c r="AE101" s="5" t="n"/>
       <c r="AF101" s="5" t="n"/>
       <c r="AG101" s="5" t="n"/>
+      <c r="AH101" s="5" t="n"/>
+      <c r="AI101" s="5" t="n"/>
+      <c r="AJ101" s="5" t="n"/>
+      <c r="AK101" s="5" t="n"/>
+      <c r="AL101" s="5" t="n"/>
+      <c r="AM101" s="5" t="n"/>
+      <c r="AN101" s="5" t="n"/>
+      <c r="AO101" s="5" t="n"/>
+      <c r="AP101" s="5" t="n"/>
+      <c r="AQ101" s="5" t="n"/>
+      <c r="AR101" s="5" t="n"/>
+      <c r="AS101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n"/>
@@ -4205,6 +5477,18 @@
       <c r="AE102" s="3" t="n"/>
       <c r="AF102" s="3" t="n"/>
       <c r="AG102" s="3" t="n"/>
+      <c r="AH102" s="3" t="n"/>
+      <c r="AI102" s="3" t="n"/>
+      <c r="AJ102" s="3" t="n"/>
+      <c r="AK102" s="3" t="n"/>
+      <c r="AL102" s="3" t="n"/>
+      <c r="AM102" s="3" t="n"/>
+      <c r="AN102" s="3" t="n"/>
+      <c r="AO102" s="3" t="n"/>
+      <c r="AP102" s="3" t="n"/>
+      <c r="AQ102" s="3" t="n"/>
+      <c r="AR102" s="3" t="n"/>
+      <c r="AS102" s="3" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n"/>
@@ -4240,6 +5524,18 @@
       <c r="AE103" s="5" t="n"/>
       <c r="AF103" s="5" t="n"/>
       <c r="AG103" s="5" t="n"/>
+      <c r="AH103" s="5" t="n"/>
+      <c r="AI103" s="5" t="n"/>
+      <c r="AJ103" s="5" t="n"/>
+      <c r="AK103" s="5" t="n"/>
+      <c r="AL103" s="5" t="n"/>
+      <c r="AM103" s="5" t="n"/>
+      <c r="AN103" s="5" t="n"/>
+      <c r="AO103" s="5" t="n"/>
+      <c r="AP103" s="5" t="n"/>
+      <c r="AQ103" s="5" t="n"/>
+      <c r="AR103" s="5" t="n"/>
+      <c r="AS103" s="5" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n"/>
@@ -4275,6 +5571,18 @@
       <c r="AE104" s="3" t="n"/>
       <c r="AF104" s="3" t="n"/>
       <c r="AG104" s="3" t="n"/>
+      <c r="AH104" s="3" t="n"/>
+      <c r="AI104" s="3" t="n"/>
+      <c r="AJ104" s="3" t="n"/>
+      <c r="AK104" s="3" t="n"/>
+      <c r="AL104" s="3" t="n"/>
+      <c r="AM104" s="3" t="n"/>
+      <c r="AN104" s="3" t="n"/>
+      <c r="AO104" s="3" t="n"/>
+      <c r="AP104" s="3" t="n"/>
+      <c r="AQ104" s="3" t="n"/>
+      <c r="AR104" s="3" t="n"/>
+      <c r="AS104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n"/>
@@ -4310,6 +5618,18 @@
       <c r="AE105" s="5" t="n"/>
       <c r="AF105" s="5" t="n"/>
       <c r="AG105" s="5" t="n"/>
+      <c r="AH105" s="5" t="n"/>
+      <c r="AI105" s="5" t="n"/>
+      <c r="AJ105" s="5" t="n"/>
+      <c r="AK105" s="5" t="n"/>
+      <c r="AL105" s="5" t="n"/>
+      <c r="AM105" s="5" t="n"/>
+      <c r="AN105" s="5" t="n"/>
+      <c r="AO105" s="5" t="n"/>
+      <c r="AP105" s="5" t="n"/>
+      <c r="AQ105" s="5" t="n"/>
+      <c r="AR105" s="5" t="n"/>
+      <c r="AS105" s="5" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
@@ -4345,6 +5665,18 @@
       <c r="AE106" s="3" t="n"/>
       <c r="AF106" s="3" t="n"/>
       <c r="AG106" s="3" t="n"/>
+      <c r="AH106" s="3" t="n"/>
+      <c r="AI106" s="3" t="n"/>
+      <c r="AJ106" s="3" t="n"/>
+      <c r="AK106" s="3" t="n"/>
+      <c r="AL106" s="3" t="n"/>
+      <c r="AM106" s="3" t="n"/>
+      <c r="AN106" s="3" t="n"/>
+      <c r="AO106" s="3" t="n"/>
+      <c r="AP106" s="3" t="n"/>
+      <c r="AQ106" s="3" t="n"/>
+      <c r="AR106" s="3" t="n"/>
+      <c r="AS106" s="3" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n"/>
@@ -4380,6 +5712,18 @@
       <c r="AE107" s="5" t="n"/>
       <c r="AF107" s="5" t="n"/>
       <c r="AG107" s="5" t="n"/>
+      <c r="AH107" s="5" t="n"/>
+      <c r="AI107" s="5" t="n"/>
+      <c r="AJ107" s="5" t="n"/>
+      <c r="AK107" s="5" t="n"/>
+      <c r="AL107" s="5" t="n"/>
+      <c r="AM107" s="5" t="n"/>
+      <c r="AN107" s="5" t="n"/>
+      <c r="AO107" s="5" t="n"/>
+      <c r="AP107" s="5" t="n"/>
+      <c r="AQ107" s="5" t="n"/>
+      <c r="AR107" s="5" t="n"/>
+      <c r="AS107" s="5" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n"/>
@@ -4415,6 +5759,18 @@
       <c r="AE108" s="3" t="n"/>
       <c r="AF108" s="3" t="n"/>
       <c r="AG108" s="3" t="n"/>
+      <c r="AH108" s="3" t="n"/>
+      <c r="AI108" s="3" t="n"/>
+      <c r="AJ108" s="3" t="n"/>
+      <c r="AK108" s="3" t="n"/>
+      <c r="AL108" s="3" t="n"/>
+      <c r="AM108" s="3" t="n"/>
+      <c r="AN108" s="3" t="n"/>
+      <c r="AO108" s="3" t="n"/>
+      <c r="AP108" s="3" t="n"/>
+      <c r="AQ108" s="3" t="n"/>
+      <c r="AR108" s="3" t="n"/>
+      <c r="AS108" s="3" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n"/>
@@ -4450,6 +5806,18 @@
       <c r="AE109" s="5" t="n"/>
       <c r="AF109" s="5" t="n"/>
       <c r="AG109" s="5" t="n"/>
+      <c r="AH109" s="5" t="n"/>
+      <c r="AI109" s="5" t="n"/>
+      <c r="AJ109" s="5" t="n"/>
+      <c r="AK109" s="5" t="n"/>
+      <c r="AL109" s="5" t="n"/>
+      <c r="AM109" s="5" t="n"/>
+      <c r="AN109" s="5" t="n"/>
+      <c r="AO109" s="5" t="n"/>
+      <c r="AP109" s="5" t="n"/>
+      <c r="AQ109" s="5" t="n"/>
+      <c r="AR109" s="5" t="n"/>
+      <c r="AS109" s="5" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n"/>
@@ -4485,6 +5853,18 @@
       <c r="AE110" s="3" t="n"/>
       <c r="AF110" s="3" t="n"/>
       <c r="AG110" s="3" t="n"/>
+      <c r="AH110" s="3" t="n"/>
+      <c r="AI110" s="3" t="n"/>
+      <c r="AJ110" s="3" t="n"/>
+      <c r="AK110" s="3" t="n"/>
+      <c r="AL110" s="3" t="n"/>
+      <c r="AM110" s="3" t="n"/>
+      <c r="AN110" s="3" t="n"/>
+      <c r="AO110" s="3" t="n"/>
+      <c r="AP110" s="3" t="n"/>
+      <c r="AQ110" s="3" t="n"/>
+      <c r="AR110" s="3" t="n"/>
+      <c r="AS110" s="3" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n"/>
@@ -4520,6 +5900,18 @@
       <c r="AE111" s="5" t="n"/>
       <c r="AF111" s="5" t="n"/>
       <c r="AG111" s="5" t="n"/>
+      <c r="AH111" s="5" t="n"/>
+      <c r="AI111" s="5" t="n"/>
+      <c r="AJ111" s="5" t="n"/>
+      <c r="AK111" s="5" t="n"/>
+      <c r="AL111" s="5" t="n"/>
+      <c r="AM111" s="5" t="n"/>
+      <c r="AN111" s="5" t="n"/>
+      <c r="AO111" s="5" t="n"/>
+      <c r="AP111" s="5" t="n"/>
+      <c r="AQ111" s="5" t="n"/>
+      <c r="AR111" s="5" t="n"/>
+      <c r="AS111" s="5" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n"/>
@@ -4555,6 +5947,18 @@
       <c r="AE112" s="3" t="n"/>
       <c r="AF112" s="3" t="n"/>
       <c r="AG112" s="3" t="n"/>
+      <c r="AH112" s="3" t="n"/>
+      <c r="AI112" s="3" t="n"/>
+      <c r="AJ112" s="3" t="n"/>
+      <c r="AK112" s="3" t="n"/>
+      <c r="AL112" s="3" t="n"/>
+      <c r="AM112" s="3" t="n"/>
+      <c r="AN112" s="3" t="n"/>
+      <c r="AO112" s="3" t="n"/>
+      <c r="AP112" s="3" t="n"/>
+      <c r="AQ112" s="3" t="n"/>
+      <c r="AR112" s="3" t="n"/>
+      <c r="AS112" s="3" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n"/>
@@ -4590,6 +5994,18 @@
       <c r="AE113" s="5" t="n"/>
       <c r="AF113" s="5" t="n"/>
       <c r="AG113" s="5" t="n"/>
+      <c r="AH113" s="5" t="n"/>
+      <c r="AI113" s="5" t="n"/>
+      <c r="AJ113" s="5" t="n"/>
+      <c r="AK113" s="5" t="n"/>
+      <c r="AL113" s="5" t="n"/>
+      <c r="AM113" s="5" t="n"/>
+      <c r="AN113" s="5" t="n"/>
+      <c r="AO113" s="5" t="n"/>
+      <c r="AP113" s="5" t="n"/>
+      <c r="AQ113" s="5" t="n"/>
+      <c r="AR113" s="5" t="n"/>
+      <c r="AS113" s="5" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n"/>
@@ -4625,6 +6041,18 @@
       <c r="AE114" s="3" t="n"/>
       <c r="AF114" s="3" t="n"/>
       <c r="AG114" s="3" t="n"/>
+      <c r="AH114" s="3" t="n"/>
+      <c r="AI114" s="3" t="n"/>
+      <c r="AJ114" s="3" t="n"/>
+      <c r="AK114" s="3" t="n"/>
+      <c r="AL114" s="3" t="n"/>
+      <c r="AM114" s="3" t="n"/>
+      <c r="AN114" s="3" t="n"/>
+      <c r="AO114" s="3" t="n"/>
+      <c r="AP114" s="3" t="n"/>
+      <c r="AQ114" s="3" t="n"/>
+      <c r="AR114" s="3" t="n"/>
+      <c r="AS114" s="3" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n"/>
@@ -4660,6 +6088,18 @@
       <c r="AE115" s="5" t="n"/>
       <c r="AF115" s="5" t="n"/>
       <c r="AG115" s="5" t="n"/>
+      <c r="AH115" s="5" t="n"/>
+      <c r="AI115" s="5" t="n"/>
+      <c r="AJ115" s="5" t="n"/>
+      <c r="AK115" s="5" t="n"/>
+      <c r="AL115" s="5" t="n"/>
+      <c r="AM115" s="5" t="n"/>
+      <c r="AN115" s="5" t="n"/>
+      <c r="AO115" s="5" t="n"/>
+      <c r="AP115" s="5" t="n"/>
+      <c r="AQ115" s="5" t="n"/>
+      <c r="AR115" s="5" t="n"/>
+      <c r="AS115" s="5" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n"/>
@@ -4695,6 +6135,18 @@
       <c r="AE116" s="3" t="n"/>
       <c r="AF116" s="3" t="n"/>
       <c r="AG116" s="3" t="n"/>
+      <c r="AH116" s="3" t="n"/>
+      <c r="AI116" s="3" t="n"/>
+      <c r="AJ116" s="3" t="n"/>
+      <c r="AK116" s="3" t="n"/>
+      <c r="AL116" s="3" t="n"/>
+      <c r="AM116" s="3" t="n"/>
+      <c r="AN116" s="3" t="n"/>
+      <c r="AO116" s="3" t="n"/>
+      <c r="AP116" s="3" t="n"/>
+      <c r="AQ116" s="3" t="n"/>
+      <c r="AR116" s="3" t="n"/>
+      <c r="AS116" s="3" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n"/>
@@ -4730,6 +6182,18 @@
       <c r="AE117" s="5" t="n"/>
       <c r="AF117" s="5" t="n"/>
       <c r="AG117" s="5" t="n"/>
+      <c r="AH117" s="5" t="n"/>
+      <c r="AI117" s="5" t="n"/>
+      <c r="AJ117" s="5" t="n"/>
+      <c r="AK117" s="5" t="n"/>
+      <c r="AL117" s="5" t="n"/>
+      <c r="AM117" s="5" t="n"/>
+      <c r="AN117" s="5" t="n"/>
+      <c r="AO117" s="5" t="n"/>
+      <c r="AP117" s="5" t="n"/>
+      <c r="AQ117" s="5" t="n"/>
+      <c r="AR117" s="5" t="n"/>
+      <c r="AS117" s="5" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n"/>
@@ -4765,6 +6229,18 @@
       <c r="AE118" s="3" t="n"/>
       <c r="AF118" s="3" t="n"/>
       <c r="AG118" s="3" t="n"/>
+      <c r="AH118" s="3" t="n"/>
+      <c r="AI118" s="3" t="n"/>
+      <c r="AJ118" s="3" t="n"/>
+      <c r="AK118" s="3" t="n"/>
+      <c r="AL118" s="3" t="n"/>
+      <c r="AM118" s="3" t="n"/>
+      <c r="AN118" s="3" t="n"/>
+      <c r="AO118" s="3" t="n"/>
+      <c r="AP118" s="3" t="n"/>
+      <c r="AQ118" s="3" t="n"/>
+      <c r="AR118" s="3" t="n"/>
+      <c r="AS118" s="3" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n"/>
@@ -4800,6 +6276,18 @@
       <c r="AE119" s="5" t="n"/>
       <c r="AF119" s="5" t="n"/>
       <c r="AG119" s="5" t="n"/>
+      <c r="AH119" s="5" t="n"/>
+      <c r="AI119" s="5" t="n"/>
+      <c r="AJ119" s="5" t="n"/>
+      <c r="AK119" s="5" t="n"/>
+      <c r="AL119" s="5" t="n"/>
+      <c r="AM119" s="5" t="n"/>
+      <c r="AN119" s="5" t="n"/>
+      <c r="AO119" s="5" t="n"/>
+      <c r="AP119" s="5" t="n"/>
+      <c r="AQ119" s="5" t="n"/>
+      <c r="AR119" s="5" t="n"/>
+      <c r="AS119" s="5" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n"/>
@@ -4835,6 +6323,18 @@
       <c r="AE120" s="3" t="n"/>
       <c r="AF120" s="3" t="n"/>
       <c r="AG120" s="3" t="n"/>
+      <c r="AH120" s="3" t="n"/>
+      <c r="AI120" s="3" t="n"/>
+      <c r="AJ120" s="3" t="n"/>
+      <c r="AK120" s="3" t="n"/>
+      <c r="AL120" s="3" t="n"/>
+      <c r="AM120" s="3" t="n"/>
+      <c r="AN120" s="3" t="n"/>
+      <c r="AO120" s="3" t="n"/>
+      <c r="AP120" s="3" t="n"/>
+      <c r="AQ120" s="3" t="n"/>
+      <c r="AR120" s="3" t="n"/>
+      <c r="AS120" s="3" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n"/>
@@ -4870,6 +6370,18 @@
       <c r="AE121" s="5" t="n"/>
       <c r="AF121" s="5" t="n"/>
       <c r="AG121" s="5" t="n"/>
+      <c r="AH121" s="5" t="n"/>
+      <c r="AI121" s="5" t="n"/>
+      <c r="AJ121" s="5" t="n"/>
+      <c r="AK121" s="5" t="n"/>
+      <c r="AL121" s="5" t="n"/>
+      <c r="AM121" s="5" t="n"/>
+      <c r="AN121" s="5" t="n"/>
+      <c r="AO121" s="5" t="n"/>
+      <c r="AP121" s="5" t="n"/>
+      <c r="AQ121" s="5" t="n"/>
+      <c r="AR121" s="5" t="n"/>
+      <c r="AS121" s="5" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n"/>
@@ -4905,6 +6417,18 @@
       <c r="AE122" s="3" t="n"/>
       <c r="AF122" s="3" t="n"/>
       <c r="AG122" s="3" t="n"/>
+      <c r="AH122" s="3" t="n"/>
+      <c r="AI122" s="3" t="n"/>
+      <c r="AJ122" s="3" t="n"/>
+      <c r="AK122" s="3" t="n"/>
+      <c r="AL122" s="3" t="n"/>
+      <c r="AM122" s="3" t="n"/>
+      <c r="AN122" s="3" t="n"/>
+      <c r="AO122" s="3" t="n"/>
+      <c r="AP122" s="3" t="n"/>
+      <c r="AQ122" s="3" t="n"/>
+      <c r="AR122" s="3" t="n"/>
+      <c r="AS122" s="3" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="n"/>
@@ -4940,6 +6464,18 @@
       <c r="AE123" s="5" t="n"/>
       <c r="AF123" s="5" t="n"/>
       <c r="AG123" s="5" t="n"/>
+      <c r="AH123" s="5" t="n"/>
+      <c r="AI123" s="5" t="n"/>
+      <c r="AJ123" s="5" t="n"/>
+      <c r="AK123" s="5" t="n"/>
+      <c r="AL123" s="5" t="n"/>
+      <c r="AM123" s="5" t="n"/>
+      <c r="AN123" s="5" t="n"/>
+      <c r="AO123" s="5" t="n"/>
+      <c r="AP123" s="5" t="n"/>
+      <c r="AQ123" s="5" t="n"/>
+      <c r="AR123" s="5" t="n"/>
+      <c r="AS123" s="5" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n"/>
@@ -4975,6 +6511,18 @@
       <c r="AE124" s="3" t="n"/>
       <c r="AF124" s="3" t="n"/>
       <c r="AG124" s="3" t="n"/>
+      <c r="AH124" s="3" t="n"/>
+      <c r="AI124" s="3" t="n"/>
+      <c r="AJ124" s="3" t="n"/>
+      <c r="AK124" s="3" t="n"/>
+      <c r="AL124" s="3" t="n"/>
+      <c r="AM124" s="3" t="n"/>
+      <c r="AN124" s="3" t="n"/>
+      <c r="AO124" s="3" t="n"/>
+      <c r="AP124" s="3" t="n"/>
+      <c r="AQ124" s="3" t="n"/>
+      <c r="AR124" s="3" t="n"/>
+      <c r="AS124" s="3" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n"/>
@@ -5010,6 +6558,18 @@
       <c r="AE125" s="5" t="n"/>
       <c r="AF125" s="5" t="n"/>
       <c r="AG125" s="5" t="n"/>
+      <c r="AH125" s="5" t="n"/>
+      <c r="AI125" s="5" t="n"/>
+      <c r="AJ125" s="5" t="n"/>
+      <c r="AK125" s="5" t="n"/>
+      <c r="AL125" s="5" t="n"/>
+      <c r="AM125" s="5" t="n"/>
+      <c r="AN125" s="5" t="n"/>
+      <c r="AO125" s="5" t="n"/>
+      <c r="AP125" s="5" t="n"/>
+      <c r="AQ125" s="5" t="n"/>
+      <c r="AR125" s="5" t="n"/>
+      <c r="AS125" s="5" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n"/>
@@ -5045,6 +6605,18 @@
       <c r="AE126" s="3" t="n"/>
       <c r="AF126" s="3" t="n"/>
       <c r="AG126" s="3" t="n"/>
+      <c r="AH126" s="3" t="n"/>
+      <c r="AI126" s="3" t="n"/>
+      <c r="AJ126" s="3" t="n"/>
+      <c r="AK126" s="3" t="n"/>
+      <c r="AL126" s="3" t="n"/>
+      <c r="AM126" s="3" t="n"/>
+      <c r="AN126" s="3" t="n"/>
+      <c r="AO126" s="3" t="n"/>
+      <c r="AP126" s="3" t="n"/>
+      <c r="AQ126" s="3" t="n"/>
+      <c r="AR126" s="3" t="n"/>
+      <c r="AS126" s="3" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n"/>
@@ -5080,6 +6652,18 @@
       <c r="AE127" s="5" t="n"/>
       <c r="AF127" s="5" t="n"/>
       <c r="AG127" s="5" t="n"/>
+      <c r="AH127" s="5" t="n"/>
+      <c r="AI127" s="5" t="n"/>
+      <c r="AJ127" s="5" t="n"/>
+      <c r="AK127" s="5" t="n"/>
+      <c r="AL127" s="5" t="n"/>
+      <c r="AM127" s="5" t="n"/>
+      <c r="AN127" s="5" t="n"/>
+      <c r="AO127" s="5" t="n"/>
+      <c r="AP127" s="5" t="n"/>
+      <c r="AQ127" s="5" t="n"/>
+      <c r="AR127" s="5" t="n"/>
+      <c r="AS127" s="5" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
@@ -5115,6 +6699,18 @@
       <c r="AE128" s="3" t="n"/>
       <c r="AF128" s="3" t="n"/>
       <c r="AG128" s="3" t="n"/>
+      <c r="AH128" s="3" t="n"/>
+      <c r="AI128" s="3" t="n"/>
+      <c r="AJ128" s="3" t="n"/>
+      <c r="AK128" s="3" t="n"/>
+      <c r="AL128" s="3" t="n"/>
+      <c r="AM128" s="3" t="n"/>
+      <c r="AN128" s="3" t="n"/>
+      <c r="AO128" s="3" t="n"/>
+      <c r="AP128" s="3" t="n"/>
+      <c r="AQ128" s="3" t="n"/>
+      <c r="AR128" s="3" t="n"/>
+      <c r="AS128" s="3" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="n"/>
@@ -5150,6 +6746,18 @@
       <c r="AE129" s="5" t="n"/>
       <c r="AF129" s="5" t="n"/>
       <c r="AG129" s="5" t="n"/>
+      <c r="AH129" s="5" t="n"/>
+      <c r="AI129" s="5" t="n"/>
+      <c r="AJ129" s="5" t="n"/>
+      <c r="AK129" s="5" t="n"/>
+      <c r="AL129" s="5" t="n"/>
+      <c r="AM129" s="5" t="n"/>
+      <c r="AN129" s="5" t="n"/>
+      <c r="AO129" s="5" t="n"/>
+      <c r="AP129" s="5" t="n"/>
+      <c r="AQ129" s="5" t="n"/>
+      <c r="AR129" s="5" t="n"/>
+      <c r="AS129" s="5" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n"/>
@@ -5185,6 +6793,18 @@
       <c r="AE130" s="3" t="n"/>
       <c r="AF130" s="3" t="n"/>
       <c r="AG130" s="3" t="n"/>
+      <c r="AH130" s="3" t="n"/>
+      <c r="AI130" s="3" t="n"/>
+      <c r="AJ130" s="3" t="n"/>
+      <c r="AK130" s="3" t="n"/>
+      <c r="AL130" s="3" t="n"/>
+      <c r="AM130" s="3" t="n"/>
+      <c r="AN130" s="3" t="n"/>
+      <c r="AO130" s="3" t="n"/>
+      <c r="AP130" s="3" t="n"/>
+      <c r="AQ130" s="3" t="n"/>
+      <c r="AR130" s="3" t="n"/>
+      <c r="AS130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n"/>
@@ -5220,6 +6840,18 @@
       <c r="AE131" s="5" t="n"/>
       <c r="AF131" s="5" t="n"/>
       <c r="AG131" s="5" t="n"/>
+      <c r="AH131" s="5" t="n"/>
+      <c r="AI131" s="5" t="n"/>
+      <c r="AJ131" s="5" t="n"/>
+      <c r="AK131" s="5" t="n"/>
+      <c r="AL131" s="5" t="n"/>
+      <c r="AM131" s="5" t="n"/>
+      <c r="AN131" s="5" t="n"/>
+      <c r="AO131" s="5" t="n"/>
+      <c r="AP131" s="5" t="n"/>
+      <c r="AQ131" s="5" t="n"/>
+      <c r="AR131" s="5" t="n"/>
+      <c r="AS131" s="5" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n"/>
@@ -5255,6 +6887,18 @@
       <c r="AE132" s="3" t="n"/>
       <c r="AF132" s="3" t="n"/>
       <c r="AG132" s="3" t="n"/>
+      <c r="AH132" s="3" t="n"/>
+      <c r="AI132" s="3" t="n"/>
+      <c r="AJ132" s="3" t="n"/>
+      <c r="AK132" s="3" t="n"/>
+      <c r="AL132" s="3" t="n"/>
+      <c r="AM132" s="3" t="n"/>
+      <c r="AN132" s="3" t="n"/>
+      <c r="AO132" s="3" t="n"/>
+      <c r="AP132" s="3" t="n"/>
+      <c r="AQ132" s="3" t="n"/>
+      <c r="AR132" s="3" t="n"/>
+      <c r="AS132" s="3" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n"/>
@@ -5290,6 +6934,18 @@
       <c r="AE133" s="5" t="n"/>
       <c r="AF133" s="5" t="n"/>
       <c r="AG133" s="5" t="n"/>
+      <c r="AH133" s="5" t="n"/>
+      <c r="AI133" s="5" t="n"/>
+      <c r="AJ133" s="5" t="n"/>
+      <c r="AK133" s="5" t="n"/>
+      <c r="AL133" s="5" t="n"/>
+      <c r="AM133" s="5" t="n"/>
+      <c r="AN133" s="5" t="n"/>
+      <c r="AO133" s="5" t="n"/>
+      <c r="AP133" s="5" t="n"/>
+      <c r="AQ133" s="5" t="n"/>
+      <c r="AR133" s="5" t="n"/>
+      <c r="AS133" s="5" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n"/>
@@ -5325,6 +6981,18 @@
       <c r="AE134" s="3" t="n"/>
       <c r="AF134" s="3" t="n"/>
       <c r="AG134" s="3" t="n"/>
+      <c r="AH134" s="3" t="n"/>
+      <c r="AI134" s="3" t="n"/>
+      <c r="AJ134" s="3" t="n"/>
+      <c r="AK134" s="3" t="n"/>
+      <c r="AL134" s="3" t="n"/>
+      <c r="AM134" s="3" t="n"/>
+      <c r="AN134" s="3" t="n"/>
+      <c r="AO134" s="3" t="n"/>
+      <c r="AP134" s="3" t="n"/>
+      <c r="AQ134" s="3" t="n"/>
+      <c r="AR134" s="3" t="n"/>
+      <c r="AS134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n"/>
@@ -5360,6 +7028,18 @@
       <c r="AE135" s="5" t="n"/>
       <c r="AF135" s="5" t="n"/>
       <c r="AG135" s="5" t="n"/>
+      <c r="AH135" s="5" t="n"/>
+      <c r="AI135" s="5" t="n"/>
+      <c r="AJ135" s="5" t="n"/>
+      <c r="AK135" s="5" t="n"/>
+      <c r="AL135" s="5" t="n"/>
+      <c r="AM135" s="5" t="n"/>
+      <c r="AN135" s="5" t="n"/>
+      <c r="AO135" s="5" t="n"/>
+      <c r="AP135" s="5" t="n"/>
+      <c r="AQ135" s="5" t="n"/>
+      <c r="AR135" s="5" t="n"/>
+      <c r="AS135" s="5" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n"/>
@@ -5395,6 +7075,18 @@
       <c r="AE136" s="3" t="n"/>
       <c r="AF136" s="3" t="n"/>
       <c r="AG136" s="3" t="n"/>
+      <c r="AH136" s="3" t="n"/>
+      <c r="AI136" s="3" t="n"/>
+      <c r="AJ136" s="3" t="n"/>
+      <c r="AK136" s="3" t="n"/>
+      <c r="AL136" s="3" t="n"/>
+      <c r="AM136" s="3" t="n"/>
+      <c r="AN136" s="3" t="n"/>
+      <c r="AO136" s="3" t="n"/>
+      <c r="AP136" s="3" t="n"/>
+      <c r="AQ136" s="3" t="n"/>
+      <c r="AR136" s="3" t="n"/>
+      <c r="AS136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="n"/>
@@ -5430,6 +7122,18 @@
       <c r="AE137" s="5" t="n"/>
       <c r="AF137" s="5" t="n"/>
       <c r="AG137" s="5" t="n"/>
+      <c r="AH137" s="5" t="n"/>
+      <c r="AI137" s="5" t="n"/>
+      <c r="AJ137" s="5" t="n"/>
+      <c r="AK137" s="5" t="n"/>
+      <c r="AL137" s="5" t="n"/>
+      <c r="AM137" s="5" t="n"/>
+      <c r="AN137" s="5" t="n"/>
+      <c r="AO137" s="5" t="n"/>
+      <c r="AP137" s="5" t="n"/>
+      <c r="AQ137" s="5" t="n"/>
+      <c r="AR137" s="5" t="n"/>
+      <c r="AS137" s="5" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n"/>
@@ -5465,6 +7169,18 @@
       <c r="AE138" s="3" t="n"/>
       <c r="AF138" s="3" t="n"/>
       <c r="AG138" s="3" t="n"/>
+      <c r="AH138" s="3" t="n"/>
+      <c r="AI138" s="3" t="n"/>
+      <c r="AJ138" s="3" t="n"/>
+      <c r="AK138" s="3" t="n"/>
+      <c r="AL138" s="3" t="n"/>
+      <c r="AM138" s="3" t="n"/>
+      <c r="AN138" s="3" t="n"/>
+      <c r="AO138" s="3" t="n"/>
+      <c r="AP138" s="3" t="n"/>
+      <c r="AQ138" s="3" t="n"/>
+      <c r="AR138" s="3" t="n"/>
+      <c r="AS138" s="3" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n"/>
@@ -5500,6 +7216,18 @@
       <c r="AE139" s="5" t="n"/>
       <c r="AF139" s="5" t="n"/>
       <c r="AG139" s="5" t="n"/>
+      <c r="AH139" s="5" t="n"/>
+      <c r="AI139" s="5" t="n"/>
+      <c r="AJ139" s="5" t="n"/>
+      <c r="AK139" s="5" t="n"/>
+      <c r="AL139" s="5" t="n"/>
+      <c r="AM139" s="5" t="n"/>
+      <c r="AN139" s="5" t="n"/>
+      <c r="AO139" s="5" t="n"/>
+      <c r="AP139" s="5" t="n"/>
+      <c r="AQ139" s="5" t="n"/>
+      <c r="AR139" s="5" t="n"/>
+      <c r="AS139" s="5" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n"/>
@@ -5535,6 +7263,18 @@
       <c r="AE140" s="3" t="n"/>
       <c r="AF140" s="3" t="n"/>
       <c r="AG140" s="3" t="n"/>
+      <c r="AH140" s="3" t="n"/>
+      <c r="AI140" s="3" t="n"/>
+      <c r="AJ140" s="3" t="n"/>
+      <c r="AK140" s="3" t="n"/>
+      <c r="AL140" s="3" t="n"/>
+      <c r="AM140" s="3" t="n"/>
+      <c r="AN140" s="3" t="n"/>
+      <c r="AO140" s="3" t="n"/>
+      <c r="AP140" s="3" t="n"/>
+      <c r="AQ140" s="3" t="n"/>
+      <c r="AR140" s="3" t="n"/>
+      <c r="AS140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n"/>
@@ -5570,6 +7310,18 @@
       <c r="AE141" s="5" t="n"/>
       <c r="AF141" s="5" t="n"/>
       <c r="AG141" s="5" t="n"/>
+      <c r="AH141" s="5" t="n"/>
+      <c r="AI141" s="5" t="n"/>
+      <c r="AJ141" s="5" t="n"/>
+      <c r="AK141" s="5" t="n"/>
+      <c r="AL141" s="5" t="n"/>
+      <c r="AM141" s="5" t="n"/>
+      <c r="AN141" s="5" t="n"/>
+      <c r="AO141" s="5" t="n"/>
+      <c r="AP141" s="5" t="n"/>
+      <c r="AQ141" s="5" t="n"/>
+      <c r="AR141" s="5" t="n"/>
+      <c r="AS141" s="5" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n"/>
@@ -5605,6 +7357,18 @@
       <c r="AE142" s="3" t="n"/>
       <c r="AF142" s="3" t="n"/>
       <c r="AG142" s="3" t="n"/>
+      <c r="AH142" s="3" t="n"/>
+      <c r="AI142" s="3" t="n"/>
+      <c r="AJ142" s="3" t="n"/>
+      <c r="AK142" s="3" t="n"/>
+      <c r="AL142" s="3" t="n"/>
+      <c r="AM142" s="3" t="n"/>
+      <c r="AN142" s="3" t="n"/>
+      <c r="AO142" s="3" t="n"/>
+      <c r="AP142" s="3" t="n"/>
+      <c r="AQ142" s="3" t="n"/>
+      <c r="AR142" s="3" t="n"/>
+      <c r="AS142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="n"/>
@@ -5640,6 +7404,18 @@
       <c r="AE143" s="5" t="n"/>
       <c r="AF143" s="5" t="n"/>
       <c r="AG143" s="5" t="n"/>
+      <c r="AH143" s="5" t="n"/>
+      <c r="AI143" s="5" t="n"/>
+      <c r="AJ143" s="5" t="n"/>
+      <c r="AK143" s="5" t="n"/>
+      <c r="AL143" s="5" t="n"/>
+      <c r="AM143" s="5" t="n"/>
+      <c r="AN143" s="5" t="n"/>
+      <c r="AO143" s="5" t="n"/>
+      <c r="AP143" s="5" t="n"/>
+      <c r="AQ143" s="5" t="n"/>
+      <c r="AR143" s="5" t="n"/>
+      <c r="AS143" s="5" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
@@ -5675,6 +7451,18 @@
       <c r="AE144" s="3" t="n"/>
       <c r="AF144" s="3" t="n"/>
       <c r="AG144" s="3" t="n"/>
+      <c r="AH144" s="3" t="n"/>
+      <c r="AI144" s="3" t="n"/>
+      <c r="AJ144" s="3" t="n"/>
+      <c r="AK144" s="3" t="n"/>
+      <c r="AL144" s="3" t="n"/>
+      <c r="AM144" s="3" t="n"/>
+      <c r="AN144" s="3" t="n"/>
+      <c r="AO144" s="3" t="n"/>
+      <c r="AP144" s="3" t="n"/>
+      <c r="AQ144" s="3" t="n"/>
+      <c r="AR144" s="3" t="n"/>
+      <c r="AS144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n"/>
@@ -5710,6 +7498,18 @@
       <c r="AE145" s="5" t="n"/>
       <c r="AF145" s="5" t="n"/>
       <c r="AG145" s="5" t="n"/>
+      <c r="AH145" s="5" t="n"/>
+      <c r="AI145" s="5" t="n"/>
+      <c r="AJ145" s="5" t="n"/>
+      <c r="AK145" s="5" t="n"/>
+      <c r="AL145" s="5" t="n"/>
+      <c r="AM145" s="5" t="n"/>
+      <c r="AN145" s="5" t="n"/>
+      <c r="AO145" s="5" t="n"/>
+      <c r="AP145" s="5" t="n"/>
+      <c r="AQ145" s="5" t="n"/>
+      <c r="AR145" s="5" t="n"/>
+      <c r="AS145" s="5" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n"/>
@@ -5745,6 +7545,18 @@
       <c r="AE146" s="3" t="n"/>
       <c r="AF146" s="3" t="n"/>
       <c r="AG146" s="3" t="n"/>
+      <c r="AH146" s="3" t="n"/>
+      <c r="AI146" s="3" t="n"/>
+      <c r="AJ146" s="3" t="n"/>
+      <c r="AK146" s="3" t="n"/>
+      <c r="AL146" s="3" t="n"/>
+      <c r="AM146" s="3" t="n"/>
+      <c r="AN146" s="3" t="n"/>
+      <c r="AO146" s="3" t="n"/>
+      <c r="AP146" s="3" t="n"/>
+      <c r="AQ146" s="3" t="n"/>
+      <c r="AR146" s="3" t="n"/>
+      <c r="AS146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n"/>
@@ -5780,6 +7592,18 @@
       <c r="AE147" s="5" t="n"/>
       <c r="AF147" s="5" t="n"/>
       <c r="AG147" s="5" t="n"/>
+      <c r="AH147" s="5" t="n"/>
+      <c r="AI147" s="5" t="n"/>
+      <c r="AJ147" s="5" t="n"/>
+      <c r="AK147" s="5" t="n"/>
+      <c r="AL147" s="5" t="n"/>
+      <c r="AM147" s="5" t="n"/>
+      <c r="AN147" s="5" t="n"/>
+      <c r="AO147" s="5" t="n"/>
+      <c r="AP147" s="5" t="n"/>
+      <c r="AQ147" s="5" t="n"/>
+      <c r="AR147" s="5" t="n"/>
+      <c r="AS147" s="5" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n"/>
@@ -5815,6 +7639,18 @@
       <c r="AE148" s="3" t="n"/>
       <c r="AF148" s="3" t="n"/>
       <c r="AG148" s="3" t="n"/>
+      <c r="AH148" s="3" t="n"/>
+      <c r="AI148" s="3" t="n"/>
+      <c r="AJ148" s="3" t="n"/>
+      <c r="AK148" s="3" t="n"/>
+      <c r="AL148" s="3" t="n"/>
+      <c r="AM148" s="3" t="n"/>
+      <c r="AN148" s="3" t="n"/>
+      <c r="AO148" s="3" t="n"/>
+      <c r="AP148" s="3" t="n"/>
+      <c r="AQ148" s="3" t="n"/>
+      <c r="AR148" s="3" t="n"/>
+      <c r="AS148" s="3" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="n"/>
@@ -5850,6 +7686,18 @@
       <c r="AE149" s="5" t="n"/>
       <c r="AF149" s="5" t="n"/>
       <c r="AG149" s="5" t="n"/>
+      <c r="AH149" s="5" t="n"/>
+      <c r="AI149" s="5" t="n"/>
+      <c r="AJ149" s="5" t="n"/>
+      <c r="AK149" s="5" t="n"/>
+      <c r="AL149" s="5" t="n"/>
+      <c r="AM149" s="5" t="n"/>
+      <c r="AN149" s="5" t="n"/>
+      <c r="AO149" s="5" t="n"/>
+      <c r="AP149" s="5" t="n"/>
+      <c r="AQ149" s="5" t="n"/>
+      <c r="AR149" s="5" t="n"/>
+      <c r="AS149" s="5" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n"/>
@@ -5885,6 +7733,18 @@
       <c r="AE150" s="3" t="n"/>
       <c r="AF150" s="3" t="n"/>
       <c r="AG150" s="3" t="n"/>
+      <c r="AH150" s="3" t="n"/>
+      <c r="AI150" s="3" t="n"/>
+      <c r="AJ150" s="3" t="n"/>
+      <c r="AK150" s="3" t="n"/>
+      <c r="AL150" s="3" t="n"/>
+      <c r="AM150" s="3" t="n"/>
+      <c r="AN150" s="3" t="n"/>
+      <c r="AO150" s="3" t="n"/>
+      <c r="AP150" s="3" t="n"/>
+      <c r="AQ150" s="3" t="n"/>
+      <c r="AR150" s="3" t="n"/>
+      <c r="AS150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n"/>
@@ -5920,6 +7780,18 @@
       <c r="AE151" s="5" t="n"/>
       <c r="AF151" s="5" t="n"/>
       <c r="AG151" s="5" t="n"/>
+      <c r="AH151" s="5" t="n"/>
+      <c r="AI151" s="5" t="n"/>
+      <c r="AJ151" s="5" t="n"/>
+      <c r="AK151" s="5" t="n"/>
+      <c r="AL151" s="5" t="n"/>
+      <c r="AM151" s="5" t="n"/>
+      <c r="AN151" s="5" t="n"/>
+      <c r="AO151" s="5" t="n"/>
+      <c r="AP151" s="5" t="n"/>
+      <c r="AQ151" s="5" t="n"/>
+      <c r="AR151" s="5" t="n"/>
+      <c r="AS151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>
@@ -5955,6 +7827,18 @@
       <c r="AE152" s="3" t="n"/>
       <c r="AF152" s="3" t="n"/>
       <c r="AG152" s="3" t="n"/>
+      <c r="AH152" s="3" t="n"/>
+      <c r="AI152" s="3" t="n"/>
+      <c r="AJ152" s="3" t="n"/>
+      <c r="AK152" s="3" t="n"/>
+      <c r="AL152" s="3" t="n"/>
+      <c r="AM152" s="3" t="n"/>
+      <c r="AN152" s="3" t="n"/>
+      <c r="AO152" s="3" t="n"/>
+      <c r="AP152" s="3" t="n"/>
+      <c r="AQ152" s="3" t="n"/>
+      <c r="AR152" s="3" t="n"/>
+      <c r="AS152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n"/>
@@ -5990,6 +7874,18 @@
       <c r="AE153" s="5" t="n"/>
       <c r="AF153" s="5" t="n"/>
       <c r="AG153" s="5" t="n"/>
+      <c r="AH153" s="5" t="n"/>
+      <c r="AI153" s="5" t="n"/>
+      <c r="AJ153" s="5" t="n"/>
+      <c r="AK153" s="5" t="n"/>
+      <c r="AL153" s="5" t="n"/>
+      <c r="AM153" s="5" t="n"/>
+      <c r="AN153" s="5" t="n"/>
+      <c r="AO153" s="5" t="n"/>
+      <c r="AP153" s="5" t="n"/>
+      <c r="AQ153" s="5" t="n"/>
+      <c r="AR153" s="5" t="n"/>
+      <c r="AS153" s="5" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n"/>
@@ -6025,6 +7921,18 @@
       <c r="AE154" s="3" t="n"/>
       <c r="AF154" s="3" t="n"/>
       <c r="AG154" s="3" t="n"/>
+      <c r="AH154" s="3" t="n"/>
+      <c r="AI154" s="3" t="n"/>
+      <c r="AJ154" s="3" t="n"/>
+      <c r="AK154" s="3" t="n"/>
+      <c r="AL154" s="3" t="n"/>
+      <c r="AM154" s="3" t="n"/>
+      <c r="AN154" s="3" t="n"/>
+      <c r="AO154" s="3" t="n"/>
+      <c r="AP154" s="3" t="n"/>
+      <c r="AQ154" s="3" t="n"/>
+      <c r="AR154" s="3" t="n"/>
+      <c r="AS154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n"/>
@@ -6060,6 +7968,18 @@
       <c r="AE155" s="5" t="n"/>
       <c r="AF155" s="5" t="n"/>
       <c r="AG155" s="5" t="n"/>
+      <c r="AH155" s="5" t="n"/>
+      <c r="AI155" s="5" t="n"/>
+      <c r="AJ155" s="5" t="n"/>
+      <c r="AK155" s="5" t="n"/>
+      <c r="AL155" s="5" t="n"/>
+      <c r="AM155" s="5" t="n"/>
+      <c r="AN155" s="5" t="n"/>
+      <c r="AO155" s="5" t="n"/>
+      <c r="AP155" s="5" t="n"/>
+      <c r="AQ155" s="5" t="n"/>
+      <c r="AR155" s="5" t="n"/>
+      <c r="AS155" s="5" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n"/>
@@ -6095,6 +8015,18 @@
       <c r="AE156" s="3" t="n"/>
       <c r="AF156" s="3" t="n"/>
       <c r="AG156" s="3" t="n"/>
+      <c r="AH156" s="3" t="n"/>
+      <c r="AI156" s="3" t="n"/>
+      <c r="AJ156" s="3" t="n"/>
+      <c r="AK156" s="3" t="n"/>
+      <c r="AL156" s="3" t="n"/>
+      <c r="AM156" s="3" t="n"/>
+      <c r="AN156" s="3" t="n"/>
+      <c r="AO156" s="3" t="n"/>
+      <c r="AP156" s="3" t="n"/>
+      <c r="AQ156" s="3" t="n"/>
+      <c r="AR156" s="3" t="n"/>
+      <c r="AS156" s="3" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n"/>
@@ -6130,6 +8062,18 @@
       <c r="AE157" s="5" t="n"/>
       <c r="AF157" s="5" t="n"/>
       <c r="AG157" s="5" t="n"/>
+      <c r="AH157" s="5" t="n"/>
+      <c r="AI157" s="5" t="n"/>
+      <c r="AJ157" s="5" t="n"/>
+      <c r="AK157" s="5" t="n"/>
+      <c r="AL157" s="5" t="n"/>
+      <c r="AM157" s="5" t="n"/>
+      <c r="AN157" s="5" t="n"/>
+      <c r="AO157" s="5" t="n"/>
+      <c r="AP157" s="5" t="n"/>
+      <c r="AQ157" s="5" t="n"/>
+      <c r="AR157" s="5" t="n"/>
+      <c r="AS157" s="5" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n"/>
@@ -6165,6 +8109,18 @@
       <c r="AE158" s="3" t="n"/>
       <c r="AF158" s="3" t="n"/>
       <c r="AG158" s="3" t="n"/>
+      <c r="AH158" s="3" t="n"/>
+      <c r="AI158" s="3" t="n"/>
+      <c r="AJ158" s="3" t="n"/>
+      <c r="AK158" s="3" t="n"/>
+      <c r="AL158" s="3" t="n"/>
+      <c r="AM158" s="3" t="n"/>
+      <c r="AN158" s="3" t="n"/>
+      <c r="AO158" s="3" t="n"/>
+      <c r="AP158" s="3" t="n"/>
+      <c r="AQ158" s="3" t="n"/>
+      <c r="AR158" s="3" t="n"/>
+      <c r="AS158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n"/>
@@ -6200,6 +8156,18 @@
       <c r="AE159" s="5" t="n"/>
       <c r="AF159" s="5" t="n"/>
       <c r="AG159" s="5" t="n"/>
+      <c r="AH159" s="5" t="n"/>
+      <c r="AI159" s="5" t="n"/>
+      <c r="AJ159" s="5" t="n"/>
+      <c r="AK159" s="5" t="n"/>
+      <c r="AL159" s="5" t="n"/>
+      <c r="AM159" s="5" t="n"/>
+      <c r="AN159" s="5" t="n"/>
+      <c r="AO159" s="5" t="n"/>
+      <c r="AP159" s="5" t="n"/>
+      <c r="AQ159" s="5" t="n"/>
+      <c r="AR159" s="5" t="n"/>
+      <c r="AS159" s="5" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n"/>
@@ -6235,6 +8203,18 @@
       <c r="AE160" s="3" t="n"/>
       <c r="AF160" s="3" t="n"/>
       <c r="AG160" s="3" t="n"/>
+      <c r="AH160" s="3" t="n"/>
+      <c r="AI160" s="3" t="n"/>
+      <c r="AJ160" s="3" t="n"/>
+      <c r="AK160" s="3" t="n"/>
+      <c r="AL160" s="3" t="n"/>
+      <c r="AM160" s="3" t="n"/>
+      <c r="AN160" s="3" t="n"/>
+      <c r="AO160" s="3" t="n"/>
+      <c r="AP160" s="3" t="n"/>
+      <c r="AQ160" s="3" t="n"/>
+      <c r="AR160" s="3" t="n"/>
+      <c r="AS160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n"/>
@@ -6270,6 +8250,18 @@
       <c r="AE161" s="5" t="n"/>
       <c r="AF161" s="5" t="n"/>
       <c r="AG161" s="5" t="n"/>
+      <c r="AH161" s="5" t="n"/>
+      <c r="AI161" s="5" t="n"/>
+      <c r="AJ161" s="5" t="n"/>
+      <c r="AK161" s="5" t="n"/>
+      <c r="AL161" s="5" t="n"/>
+      <c r="AM161" s="5" t="n"/>
+      <c r="AN161" s="5" t="n"/>
+      <c r="AO161" s="5" t="n"/>
+      <c r="AP161" s="5" t="n"/>
+      <c r="AQ161" s="5" t="n"/>
+      <c r="AR161" s="5" t="n"/>
+      <c r="AS161" s="5" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n"/>
@@ -6305,6 +8297,18 @@
       <c r="AE162" s="3" t="n"/>
       <c r="AF162" s="3" t="n"/>
       <c r="AG162" s="3" t="n"/>
+      <c r="AH162" s="3" t="n"/>
+      <c r="AI162" s="3" t="n"/>
+      <c r="AJ162" s="3" t="n"/>
+      <c r="AK162" s="3" t="n"/>
+      <c r="AL162" s="3" t="n"/>
+      <c r="AM162" s="3" t="n"/>
+      <c r="AN162" s="3" t="n"/>
+      <c r="AO162" s="3" t="n"/>
+      <c r="AP162" s="3" t="n"/>
+      <c r="AQ162" s="3" t="n"/>
+      <c r="AR162" s="3" t="n"/>
+      <c r="AS162" s="3" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n"/>
@@ -6340,6 +8344,18 @@
       <c r="AE163" s="5" t="n"/>
       <c r="AF163" s="5" t="n"/>
       <c r="AG163" s="5" t="n"/>
+      <c r="AH163" s="5" t="n"/>
+      <c r="AI163" s="5" t="n"/>
+      <c r="AJ163" s="5" t="n"/>
+      <c r="AK163" s="5" t="n"/>
+      <c r="AL163" s="5" t="n"/>
+      <c r="AM163" s="5" t="n"/>
+      <c r="AN163" s="5" t="n"/>
+      <c r="AO163" s="5" t="n"/>
+      <c r="AP163" s="5" t="n"/>
+      <c r="AQ163" s="5" t="n"/>
+      <c r="AR163" s="5" t="n"/>
+      <c r="AS163" s="5" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n"/>
@@ -6375,6 +8391,18 @@
       <c r="AE164" s="3" t="n"/>
       <c r="AF164" s="3" t="n"/>
       <c r="AG164" s="3" t="n"/>
+      <c r="AH164" s="3" t="n"/>
+      <c r="AI164" s="3" t="n"/>
+      <c r="AJ164" s="3" t="n"/>
+      <c r="AK164" s="3" t="n"/>
+      <c r="AL164" s="3" t="n"/>
+      <c r="AM164" s="3" t="n"/>
+      <c r="AN164" s="3" t="n"/>
+      <c r="AO164" s="3" t="n"/>
+      <c r="AP164" s="3" t="n"/>
+      <c r="AQ164" s="3" t="n"/>
+      <c r="AR164" s="3" t="n"/>
+      <c r="AS164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n"/>
@@ -6410,6 +8438,18 @@
       <c r="AE165" s="5" t="n"/>
       <c r="AF165" s="5" t="n"/>
       <c r="AG165" s="5" t="n"/>
+      <c r="AH165" s="5" t="n"/>
+      <c r="AI165" s="5" t="n"/>
+      <c r="AJ165" s="5" t="n"/>
+      <c r="AK165" s="5" t="n"/>
+      <c r="AL165" s="5" t="n"/>
+      <c r="AM165" s="5" t="n"/>
+      <c r="AN165" s="5" t="n"/>
+      <c r="AO165" s="5" t="n"/>
+      <c r="AP165" s="5" t="n"/>
+      <c r="AQ165" s="5" t="n"/>
+      <c r="AR165" s="5" t="n"/>
+      <c r="AS165" s="5" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n"/>
@@ -6445,6 +8485,18 @@
       <c r="AE166" s="3" t="n"/>
       <c r="AF166" s="3" t="n"/>
       <c r="AG166" s="3" t="n"/>
+      <c r="AH166" s="3" t="n"/>
+      <c r="AI166" s="3" t="n"/>
+      <c r="AJ166" s="3" t="n"/>
+      <c r="AK166" s="3" t="n"/>
+      <c r="AL166" s="3" t="n"/>
+      <c r="AM166" s="3" t="n"/>
+      <c r="AN166" s="3" t="n"/>
+      <c r="AO166" s="3" t="n"/>
+      <c r="AP166" s="3" t="n"/>
+      <c r="AQ166" s="3" t="n"/>
+      <c r="AR166" s="3" t="n"/>
+      <c r="AS166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n"/>
@@ -6480,6 +8532,18 @@
       <c r="AE167" s="5" t="n"/>
       <c r="AF167" s="5" t="n"/>
       <c r="AG167" s="5" t="n"/>
+      <c r="AH167" s="5" t="n"/>
+      <c r="AI167" s="5" t="n"/>
+      <c r="AJ167" s="5" t="n"/>
+      <c r="AK167" s="5" t="n"/>
+      <c r="AL167" s="5" t="n"/>
+      <c r="AM167" s="5" t="n"/>
+      <c r="AN167" s="5" t="n"/>
+      <c r="AO167" s="5" t="n"/>
+      <c r="AP167" s="5" t="n"/>
+      <c r="AQ167" s="5" t="n"/>
+      <c r="AR167" s="5" t="n"/>
+      <c r="AS167" s="5" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n"/>
@@ -6515,6 +8579,18 @@
       <c r="AE168" s="3" t="n"/>
       <c r="AF168" s="3" t="n"/>
       <c r="AG168" s="3" t="n"/>
+      <c r="AH168" s="3" t="n"/>
+      <c r="AI168" s="3" t="n"/>
+      <c r="AJ168" s="3" t="n"/>
+      <c r="AK168" s="3" t="n"/>
+      <c r="AL168" s="3" t="n"/>
+      <c r="AM168" s="3" t="n"/>
+      <c r="AN168" s="3" t="n"/>
+      <c r="AO168" s="3" t="n"/>
+      <c r="AP168" s="3" t="n"/>
+      <c r="AQ168" s="3" t="n"/>
+      <c r="AR168" s="3" t="n"/>
+      <c r="AS168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n"/>
@@ -6550,6 +8626,18 @@
       <c r="AE169" s="5" t="n"/>
       <c r="AF169" s="5" t="n"/>
       <c r="AG169" s="5" t="n"/>
+      <c r="AH169" s="5" t="n"/>
+      <c r="AI169" s="5" t="n"/>
+      <c r="AJ169" s="5" t="n"/>
+      <c r="AK169" s="5" t="n"/>
+      <c r="AL169" s="5" t="n"/>
+      <c r="AM169" s="5" t="n"/>
+      <c r="AN169" s="5" t="n"/>
+      <c r="AO169" s="5" t="n"/>
+      <c r="AP169" s="5" t="n"/>
+      <c r="AQ169" s="5" t="n"/>
+      <c r="AR169" s="5" t="n"/>
+      <c r="AS169" s="5" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
@@ -6585,6 +8673,18 @@
       <c r="AE170" s="3" t="n"/>
       <c r="AF170" s="3" t="n"/>
       <c r="AG170" s="3" t="n"/>
+      <c r="AH170" s="3" t="n"/>
+      <c r="AI170" s="3" t="n"/>
+      <c r="AJ170" s="3" t="n"/>
+      <c r="AK170" s="3" t="n"/>
+      <c r="AL170" s="3" t="n"/>
+      <c r="AM170" s="3" t="n"/>
+      <c r="AN170" s="3" t="n"/>
+      <c r="AO170" s="3" t="n"/>
+      <c r="AP170" s="3" t="n"/>
+      <c r="AQ170" s="3" t="n"/>
+      <c r="AR170" s="3" t="n"/>
+      <c r="AS170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n"/>
@@ -6620,6 +8720,18 @@
       <c r="AE171" s="5" t="n"/>
       <c r="AF171" s="5" t="n"/>
       <c r="AG171" s="5" t="n"/>
+      <c r="AH171" s="5" t="n"/>
+      <c r="AI171" s="5" t="n"/>
+      <c r="AJ171" s="5" t="n"/>
+      <c r="AK171" s="5" t="n"/>
+      <c r="AL171" s="5" t="n"/>
+      <c r="AM171" s="5" t="n"/>
+      <c r="AN171" s="5" t="n"/>
+      <c r="AO171" s="5" t="n"/>
+      <c r="AP171" s="5" t="n"/>
+      <c r="AQ171" s="5" t="n"/>
+      <c r="AR171" s="5" t="n"/>
+      <c r="AS171" s="5" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n"/>
@@ -6655,6 +8767,18 @@
       <c r="AE172" s="3" t="n"/>
       <c r="AF172" s="3" t="n"/>
       <c r="AG172" s="3" t="n"/>
+      <c r="AH172" s="3" t="n"/>
+      <c r="AI172" s="3" t="n"/>
+      <c r="AJ172" s="3" t="n"/>
+      <c r="AK172" s="3" t="n"/>
+      <c r="AL172" s="3" t="n"/>
+      <c r="AM172" s="3" t="n"/>
+      <c r="AN172" s="3" t="n"/>
+      <c r="AO172" s="3" t="n"/>
+      <c r="AP172" s="3" t="n"/>
+      <c r="AQ172" s="3" t="n"/>
+      <c r="AR172" s="3" t="n"/>
+      <c r="AS172" s="3" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n"/>
@@ -6690,6 +8814,18 @@
       <c r="AE173" s="5" t="n"/>
       <c r="AF173" s="5" t="n"/>
       <c r="AG173" s="5" t="n"/>
+      <c r="AH173" s="5" t="n"/>
+      <c r="AI173" s="5" t="n"/>
+      <c r="AJ173" s="5" t="n"/>
+      <c r="AK173" s="5" t="n"/>
+      <c r="AL173" s="5" t="n"/>
+      <c r="AM173" s="5" t="n"/>
+      <c r="AN173" s="5" t="n"/>
+      <c r="AO173" s="5" t="n"/>
+      <c r="AP173" s="5" t="n"/>
+      <c r="AQ173" s="5" t="n"/>
+      <c r="AR173" s="5" t="n"/>
+      <c r="AS173" s="5" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n"/>
@@ -6725,6 +8861,18 @@
       <c r="AE174" s="3" t="n"/>
       <c r="AF174" s="3" t="n"/>
       <c r="AG174" s="3" t="n"/>
+      <c r="AH174" s="3" t="n"/>
+      <c r="AI174" s="3" t="n"/>
+      <c r="AJ174" s="3" t="n"/>
+      <c r="AK174" s="3" t="n"/>
+      <c r="AL174" s="3" t="n"/>
+      <c r="AM174" s="3" t="n"/>
+      <c r="AN174" s="3" t="n"/>
+      <c r="AO174" s="3" t="n"/>
+      <c r="AP174" s="3" t="n"/>
+      <c r="AQ174" s="3" t="n"/>
+      <c r="AR174" s="3" t="n"/>
+      <c r="AS174" s="3" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n"/>
@@ -6760,6 +8908,18 @@
       <c r="AE175" s="5" t="n"/>
       <c r="AF175" s="5" t="n"/>
       <c r="AG175" s="5" t="n"/>
+      <c r="AH175" s="5" t="n"/>
+      <c r="AI175" s="5" t="n"/>
+      <c r="AJ175" s="5" t="n"/>
+      <c r="AK175" s="5" t="n"/>
+      <c r="AL175" s="5" t="n"/>
+      <c r="AM175" s="5" t="n"/>
+      <c r="AN175" s="5" t="n"/>
+      <c r="AO175" s="5" t="n"/>
+      <c r="AP175" s="5" t="n"/>
+      <c r="AQ175" s="5" t="n"/>
+      <c r="AR175" s="5" t="n"/>
+      <c r="AS175" s="5" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
@@ -6795,6 +8955,18 @@
       <c r="AE176" s="3" t="n"/>
       <c r="AF176" s="3" t="n"/>
       <c r="AG176" s="3" t="n"/>
+      <c r="AH176" s="3" t="n"/>
+      <c r="AI176" s="3" t="n"/>
+      <c r="AJ176" s="3" t="n"/>
+      <c r="AK176" s="3" t="n"/>
+      <c r="AL176" s="3" t="n"/>
+      <c r="AM176" s="3" t="n"/>
+      <c r="AN176" s="3" t="n"/>
+      <c r="AO176" s="3" t="n"/>
+      <c r="AP176" s="3" t="n"/>
+      <c r="AQ176" s="3" t="n"/>
+      <c r="AR176" s="3" t="n"/>
+      <c r="AS176" s="3" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n"/>
@@ -6830,6 +9002,18 @@
       <c r="AE177" s="5" t="n"/>
       <c r="AF177" s="5" t="n"/>
       <c r="AG177" s="5" t="n"/>
+      <c r="AH177" s="5" t="n"/>
+      <c r="AI177" s="5" t="n"/>
+      <c r="AJ177" s="5" t="n"/>
+      <c r="AK177" s="5" t="n"/>
+      <c r="AL177" s="5" t="n"/>
+      <c r="AM177" s="5" t="n"/>
+      <c r="AN177" s="5" t="n"/>
+      <c r="AO177" s="5" t="n"/>
+      <c r="AP177" s="5" t="n"/>
+      <c r="AQ177" s="5" t="n"/>
+      <c r="AR177" s="5" t="n"/>
+      <c r="AS177" s="5" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n"/>
@@ -6865,6 +9049,18 @@
       <c r="AE178" s="3" t="n"/>
       <c r="AF178" s="3" t="n"/>
       <c r="AG178" s="3" t="n"/>
+      <c r="AH178" s="3" t="n"/>
+      <c r="AI178" s="3" t="n"/>
+      <c r="AJ178" s="3" t="n"/>
+      <c r="AK178" s="3" t="n"/>
+      <c r="AL178" s="3" t="n"/>
+      <c r="AM178" s="3" t="n"/>
+      <c r="AN178" s="3" t="n"/>
+      <c r="AO178" s="3" t="n"/>
+      <c r="AP178" s="3" t="n"/>
+      <c r="AQ178" s="3" t="n"/>
+      <c r="AR178" s="3" t="n"/>
+      <c r="AS178" s="3" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n"/>
@@ -6900,6 +9096,18 @@
       <c r="AE179" s="5" t="n"/>
       <c r="AF179" s="5" t="n"/>
       <c r="AG179" s="5" t="n"/>
+      <c r="AH179" s="5" t="n"/>
+      <c r="AI179" s="5" t="n"/>
+      <c r="AJ179" s="5" t="n"/>
+      <c r="AK179" s="5" t="n"/>
+      <c r="AL179" s="5" t="n"/>
+      <c r="AM179" s="5" t="n"/>
+      <c r="AN179" s="5" t="n"/>
+      <c r="AO179" s="5" t="n"/>
+      <c r="AP179" s="5" t="n"/>
+      <c r="AQ179" s="5" t="n"/>
+      <c r="AR179" s="5" t="n"/>
+      <c r="AS179" s="5" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n"/>
@@ -6935,6 +9143,18 @@
       <c r="AE180" s="3" t="n"/>
       <c r="AF180" s="3" t="n"/>
       <c r="AG180" s="3" t="n"/>
+      <c r="AH180" s="3" t="n"/>
+      <c r="AI180" s="3" t="n"/>
+      <c r="AJ180" s="3" t="n"/>
+      <c r="AK180" s="3" t="n"/>
+      <c r="AL180" s="3" t="n"/>
+      <c r="AM180" s="3" t="n"/>
+      <c r="AN180" s="3" t="n"/>
+      <c r="AO180" s="3" t="n"/>
+      <c r="AP180" s="3" t="n"/>
+      <c r="AQ180" s="3" t="n"/>
+      <c r="AR180" s="3" t="n"/>
+      <c r="AS180" s="3" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n"/>
@@ -6970,6 +9190,18 @@
       <c r="AE181" s="5" t="n"/>
       <c r="AF181" s="5" t="n"/>
       <c r="AG181" s="5" t="n"/>
+      <c r="AH181" s="5" t="n"/>
+      <c r="AI181" s="5" t="n"/>
+      <c r="AJ181" s="5" t="n"/>
+      <c r="AK181" s="5" t="n"/>
+      <c r="AL181" s="5" t="n"/>
+      <c r="AM181" s="5" t="n"/>
+      <c r="AN181" s="5" t="n"/>
+      <c r="AO181" s="5" t="n"/>
+      <c r="AP181" s="5" t="n"/>
+      <c r="AQ181" s="5" t="n"/>
+      <c r="AR181" s="5" t="n"/>
+      <c r="AS181" s="5" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n"/>
@@ -7005,6 +9237,18 @@
       <c r="AE182" s="3" t="n"/>
       <c r="AF182" s="3" t="n"/>
       <c r="AG182" s="3" t="n"/>
+      <c r="AH182" s="3" t="n"/>
+      <c r="AI182" s="3" t="n"/>
+      <c r="AJ182" s="3" t="n"/>
+      <c r="AK182" s="3" t="n"/>
+      <c r="AL182" s="3" t="n"/>
+      <c r="AM182" s="3" t="n"/>
+      <c r="AN182" s="3" t="n"/>
+      <c r="AO182" s="3" t="n"/>
+      <c r="AP182" s="3" t="n"/>
+      <c r="AQ182" s="3" t="n"/>
+      <c r="AR182" s="3" t="n"/>
+      <c r="AS182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="n"/>
@@ -7040,6 +9284,18 @@
       <c r="AE183" s="5" t="n"/>
       <c r="AF183" s="5" t="n"/>
       <c r="AG183" s="5" t="n"/>
+      <c r="AH183" s="5" t="n"/>
+      <c r="AI183" s="5" t="n"/>
+      <c r="AJ183" s="5" t="n"/>
+      <c r="AK183" s="5" t="n"/>
+      <c r="AL183" s="5" t="n"/>
+      <c r="AM183" s="5" t="n"/>
+      <c r="AN183" s="5" t="n"/>
+      <c r="AO183" s="5" t="n"/>
+      <c r="AP183" s="5" t="n"/>
+      <c r="AQ183" s="5" t="n"/>
+      <c r="AR183" s="5" t="n"/>
+      <c r="AS183" s="5" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n"/>
@@ -7075,6 +9331,18 @@
       <c r="AE184" s="3" t="n"/>
       <c r="AF184" s="3" t="n"/>
       <c r="AG184" s="3" t="n"/>
+      <c r="AH184" s="3" t="n"/>
+      <c r="AI184" s="3" t="n"/>
+      <c r="AJ184" s="3" t="n"/>
+      <c r="AK184" s="3" t="n"/>
+      <c r="AL184" s="3" t="n"/>
+      <c r="AM184" s="3" t="n"/>
+      <c r="AN184" s="3" t="n"/>
+      <c r="AO184" s="3" t="n"/>
+      <c r="AP184" s="3" t="n"/>
+      <c r="AQ184" s="3" t="n"/>
+      <c r="AR184" s="3" t="n"/>
+      <c r="AS184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n"/>
@@ -7110,6 +9378,18 @@
       <c r="AE185" s="5" t="n"/>
       <c r="AF185" s="5" t="n"/>
       <c r="AG185" s="5" t="n"/>
+      <c r="AH185" s="5" t="n"/>
+      <c r="AI185" s="5" t="n"/>
+      <c r="AJ185" s="5" t="n"/>
+      <c r="AK185" s="5" t="n"/>
+      <c r="AL185" s="5" t="n"/>
+      <c r="AM185" s="5" t="n"/>
+      <c r="AN185" s="5" t="n"/>
+      <c r="AO185" s="5" t="n"/>
+      <c r="AP185" s="5" t="n"/>
+      <c r="AQ185" s="5" t="n"/>
+      <c r="AR185" s="5" t="n"/>
+      <c r="AS185" s="5" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n"/>
@@ -7145,6 +9425,18 @@
       <c r="AE186" s="3" t="n"/>
       <c r="AF186" s="3" t="n"/>
       <c r="AG186" s="3" t="n"/>
+      <c r="AH186" s="3" t="n"/>
+      <c r="AI186" s="3" t="n"/>
+      <c r="AJ186" s="3" t="n"/>
+      <c r="AK186" s="3" t="n"/>
+      <c r="AL186" s="3" t="n"/>
+      <c r="AM186" s="3" t="n"/>
+      <c r="AN186" s="3" t="n"/>
+      <c r="AO186" s="3" t="n"/>
+      <c r="AP186" s="3" t="n"/>
+      <c r="AQ186" s="3" t="n"/>
+      <c r="AR186" s="3" t="n"/>
+      <c r="AS186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n"/>
@@ -7180,6 +9472,18 @@
       <c r="AE187" s="5" t="n"/>
       <c r="AF187" s="5" t="n"/>
       <c r="AG187" s="5" t="n"/>
+      <c r="AH187" s="5" t="n"/>
+      <c r="AI187" s="5" t="n"/>
+      <c r="AJ187" s="5" t="n"/>
+      <c r="AK187" s="5" t="n"/>
+      <c r="AL187" s="5" t="n"/>
+      <c r="AM187" s="5" t="n"/>
+      <c r="AN187" s="5" t="n"/>
+      <c r="AO187" s="5" t="n"/>
+      <c r="AP187" s="5" t="n"/>
+      <c r="AQ187" s="5" t="n"/>
+      <c r="AR187" s="5" t="n"/>
+      <c r="AS187" s="5" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n"/>
@@ -7215,6 +9519,18 @@
       <c r="AE188" s="3" t="n"/>
       <c r="AF188" s="3" t="n"/>
       <c r="AG188" s="3" t="n"/>
+      <c r="AH188" s="3" t="n"/>
+      <c r="AI188" s="3" t="n"/>
+      <c r="AJ188" s="3" t="n"/>
+      <c r="AK188" s="3" t="n"/>
+      <c r="AL188" s="3" t="n"/>
+      <c r="AM188" s="3" t="n"/>
+      <c r="AN188" s="3" t="n"/>
+      <c r="AO188" s="3" t="n"/>
+      <c r="AP188" s="3" t="n"/>
+      <c r="AQ188" s="3" t="n"/>
+      <c r="AR188" s="3" t="n"/>
+      <c r="AS188" s="3" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n"/>
@@ -7250,6 +9566,18 @@
       <c r="AE189" s="5" t="n"/>
       <c r="AF189" s="5" t="n"/>
       <c r="AG189" s="5" t="n"/>
+      <c r="AH189" s="5" t="n"/>
+      <c r="AI189" s="5" t="n"/>
+      <c r="AJ189" s="5" t="n"/>
+      <c r="AK189" s="5" t="n"/>
+      <c r="AL189" s="5" t="n"/>
+      <c r="AM189" s="5" t="n"/>
+      <c r="AN189" s="5" t="n"/>
+      <c r="AO189" s="5" t="n"/>
+      <c r="AP189" s="5" t="n"/>
+      <c r="AQ189" s="5" t="n"/>
+      <c r="AR189" s="5" t="n"/>
+      <c r="AS189" s="5" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n"/>
@@ -7285,6 +9613,18 @@
       <c r="AE190" s="3" t="n"/>
       <c r="AF190" s="3" t="n"/>
       <c r="AG190" s="3" t="n"/>
+      <c r="AH190" s="3" t="n"/>
+      <c r="AI190" s="3" t="n"/>
+      <c r="AJ190" s="3" t="n"/>
+      <c r="AK190" s="3" t="n"/>
+      <c r="AL190" s="3" t="n"/>
+      <c r="AM190" s="3" t="n"/>
+      <c r="AN190" s="3" t="n"/>
+      <c r="AO190" s="3" t="n"/>
+      <c r="AP190" s="3" t="n"/>
+      <c r="AQ190" s="3" t="n"/>
+      <c r="AR190" s="3" t="n"/>
+      <c r="AS190" s="3" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n"/>
@@ -7320,6 +9660,18 @@
       <c r="AE191" s="5" t="n"/>
       <c r="AF191" s="5" t="n"/>
       <c r="AG191" s="5" t="n"/>
+      <c r="AH191" s="5" t="n"/>
+      <c r="AI191" s="5" t="n"/>
+      <c r="AJ191" s="5" t="n"/>
+      <c r="AK191" s="5" t="n"/>
+      <c r="AL191" s="5" t="n"/>
+      <c r="AM191" s="5" t="n"/>
+      <c r="AN191" s="5" t="n"/>
+      <c r="AO191" s="5" t="n"/>
+      <c r="AP191" s="5" t="n"/>
+      <c r="AQ191" s="5" t="n"/>
+      <c r="AR191" s="5" t="n"/>
+      <c r="AS191" s="5" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n"/>
@@ -7355,6 +9707,18 @@
       <c r="AE192" s="3" t="n"/>
       <c r="AF192" s="3" t="n"/>
       <c r="AG192" s="3" t="n"/>
+      <c r="AH192" s="3" t="n"/>
+      <c r="AI192" s="3" t="n"/>
+      <c r="AJ192" s="3" t="n"/>
+      <c r="AK192" s="3" t="n"/>
+      <c r="AL192" s="3" t="n"/>
+      <c r="AM192" s="3" t="n"/>
+      <c r="AN192" s="3" t="n"/>
+      <c r="AO192" s="3" t="n"/>
+      <c r="AP192" s="3" t="n"/>
+      <c r="AQ192" s="3" t="n"/>
+      <c r="AR192" s="3" t="n"/>
+      <c r="AS192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="n"/>
@@ -7390,6 +9754,18 @@
       <c r="AE193" s="5" t="n"/>
       <c r="AF193" s="5" t="n"/>
       <c r="AG193" s="5" t="n"/>
+      <c r="AH193" s="5" t="n"/>
+      <c r="AI193" s="5" t="n"/>
+      <c r="AJ193" s="5" t="n"/>
+      <c r="AK193" s="5" t="n"/>
+      <c r="AL193" s="5" t="n"/>
+      <c r="AM193" s="5" t="n"/>
+      <c r="AN193" s="5" t="n"/>
+      <c r="AO193" s="5" t="n"/>
+      <c r="AP193" s="5" t="n"/>
+      <c r="AQ193" s="5" t="n"/>
+      <c r="AR193" s="5" t="n"/>
+      <c r="AS193" s="5" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n"/>
@@ -7425,6 +9801,18 @@
       <c r="AE194" s="3" t="n"/>
       <c r="AF194" s="3" t="n"/>
       <c r="AG194" s="3" t="n"/>
+      <c r="AH194" s="3" t="n"/>
+      <c r="AI194" s="3" t="n"/>
+      <c r="AJ194" s="3" t="n"/>
+      <c r="AK194" s="3" t="n"/>
+      <c r="AL194" s="3" t="n"/>
+      <c r="AM194" s="3" t="n"/>
+      <c r="AN194" s="3" t="n"/>
+      <c r="AO194" s="3" t="n"/>
+      <c r="AP194" s="3" t="n"/>
+      <c r="AQ194" s="3" t="n"/>
+      <c r="AR194" s="3" t="n"/>
+      <c r="AS194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n"/>
@@ -7460,6 +9848,18 @@
       <c r="AE195" s="5" t="n"/>
       <c r="AF195" s="5" t="n"/>
       <c r="AG195" s="5" t="n"/>
+      <c r="AH195" s="5" t="n"/>
+      <c r="AI195" s="5" t="n"/>
+      <c r="AJ195" s="5" t="n"/>
+      <c r="AK195" s="5" t="n"/>
+      <c r="AL195" s="5" t="n"/>
+      <c r="AM195" s="5" t="n"/>
+      <c r="AN195" s="5" t="n"/>
+      <c r="AO195" s="5" t="n"/>
+      <c r="AP195" s="5" t="n"/>
+      <c r="AQ195" s="5" t="n"/>
+      <c r="AR195" s="5" t="n"/>
+      <c r="AS195" s="5" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n"/>
@@ -7495,6 +9895,18 @@
       <c r="AE196" s="3" t="n"/>
       <c r="AF196" s="3" t="n"/>
       <c r="AG196" s="3" t="n"/>
+      <c r="AH196" s="3" t="n"/>
+      <c r="AI196" s="3" t="n"/>
+      <c r="AJ196" s="3" t="n"/>
+      <c r="AK196" s="3" t="n"/>
+      <c r="AL196" s="3" t="n"/>
+      <c r="AM196" s="3" t="n"/>
+      <c r="AN196" s="3" t="n"/>
+      <c r="AO196" s="3" t="n"/>
+      <c r="AP196" s="3" t="n"/>
+      <c r="AQ196" s="3" t="n"/>
+      <c r="AR196" s="3" t="n"/>
+      <c r="AS196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="n"/>
@@ -7530,6 +9942,18 @@
       <c r="AE197" s="5" t="n"/>
       <c r="AF197" s="5" t="n"/>
       <c r="AG197" s="5" t="n"/>
+      <c r="AH197" s="5" t="n"/>
+      <c r="AI197" s="5" t="n"/>
+      <c r="AJ197" s="5" t="n"/>
+      <c r="AK197" s="5" t="n"/>
+      <c r="AL197" s="5" t="n"/>
+      <c r="AM197" s="5" t="n"/>
+      <c r="AN197" s="5" t="n"/>
+      <c r="AO197" s="5" t="n"/>
+      <c r="AP197" s="5" t="n"/>
+      <c r="AQ197" s="5" t="n"/>
+      <c r="AR197" s="5" t="n"/>
+      <c r="AS197" s="5" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n"/>
@@ -7565,6 +9989,18 @@
       <c r="AE198" s="3" t="n"/>
       <c r="AF198" s="3" t="n"/>
       <c r="AG198" s="3" t="n"/>
+      <c r="AH198" s="3" t="n"/>
+      <c r="AI198" s="3" t="n"/>
+      <c r="AJ198" s="3" t="n"/>
+      <c r="AK198" s="3" t="n"/>
+      <c r="AL198" s="3" t="n"/>
+      <c r="AM198" s="3" t="n"/>
+      <c r="AN198" s="3" t="n"/>
+      <c r="AO198" s="3" t="n"/>
+      <c r="AP198" s="3" t="n"/>
+      <c r="AQ198" s="3" t="n"/>
+      <c r="AR198" s="3" t="n"/>
+      <c r="AS198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n"/>
@@ -7600,6 +10036,18 @@
       <c r="AE199" s="5" t="n"/>
       <c r="AF199" s="5" t="n"/>
       <c r="AG199" s="5" t="n"/>
+      <c r="AH199" s="5" t="n"/>
+      <c r="AI199" s="5" t="n"/>
+      <c r="AJ199" s="5" t="n"/>
+      <c r="AK199" s="5" t="n"/>
+      <c r="AL199" s="5" t="n"/>
+      <c r="AM199" s="5" t="n"/>
+      <c r="AN199" s="5" t="n"/>
+      <c r="AO199" s="5" t="n"/>
+      <c r="AP199" s="5" t="n"/>
+      <c r="AQ199" s="5" t="n"/>
+      <c r="AR199" s="5" t="n"/>
+      <c r="AS199" s="5" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n"/>
@@ -7635,6 +10083,18 @@
       <c r="AE200" s="3" t="n"/>
       <c r="AF200" s="3" t="n"/>
       <c r="AG200" s="3" t="n"/>
+      <c r="AH200" s="3" t="n"/>
+      <c r="AI200" s="3" t="n"/>
+      <c r="AJ200" s="3" t="n"/>
+      <c r="AK200" s="3" t="n"/>
+      <c r="AL200" s="3" t="n"/>
+      <c r="AM200" s="3" t="n"/>
+      <c r="AN200" s="3" t="n"/>
+      <c r="AO200" s="3" t="n"/>
+      <c r="AP200" s="3" t="n"/>
+      <c r="AQ200" s="3" t="n"/>
+      <c r="AR200" s="3" t="n"/>
+      <c r="AS200" s="3" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="n"/>
@@ -7670,6 +10130,18 @@
       <c r="AE201" s="5" t="n"/>
       <c r="AF201" s="5" t="n"/>
       <c r="AG201" s="5" t="n"/>
+      <c r="AH201" s="5" t="n"/>
+      <c r="AI201" s="5" t="n"/>
+      <c r="AJ201" s="5" t="n"/>
+      <c r="AK201" s="5" t="n"/>
+      <c r="AL201" s="5" t="n"/>
+      <c r="AM201" s="5" t="n"/>
+      <c r="AN201" s="5" t="n"/>
+      <c r="AO201" s="5" t="n"/>
+      <c r="AP201" s="5" t="n"/>
+      <c r="AQ201" s="5" t="n"/>
+      <c r="AR201" s="5" t="n"/>
+      <c r="AS201" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
